--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81739BE-CE7A-44C1-83CD-2E74C9FFF9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F165D099-D819-4A28-902F-A04AB676CC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-570" yWindow="2355" windowWidth="18315" windowHeight="11070" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -39,8 +39,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Татьяна-ПК</author>
+  </authors>
+  <commentList>
+    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{E9E9D692-ACD3-491E-8DF1-AC12E53D4B3E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Татьяна-ПК:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>исходные</t>
   </si>
@@ -100,12 +134,108 @@
       <t xml:space="preserve"> теория гравитации</t>
     </r>
   </si>
+  <si>
+    <t>микролептонных</t>
+  </si>
+  <si>
+    <t>тахионных</t>
+  </si>
+  <si>
+    <t>на величину постоянного значения</t>
+  </si>
+  <si>
+    <t>на величину постоянные значения</t>
+  </si>
+  <si>
+    <t>возможная жизненный заряд</t>
+  </si>
+  <si>
+    <t>возможно жизненный заряд</t>
+  </si>
+  <si>
+    <t>присутствуют в учения</t>
+  </si>
+  <si>
+    <t>присутствуют в учении</t>
+  </si>
+  <si>
+    <t>спиновую</t>
+  </si>
+  <si>
+    <t>спиновое</t>
+  </si>
+  <si>
+    <t>скрученой звездоведения</t>
+  </si>
+  <si>
+    <t>скрученного звездоведения</t>
+  </si>
+  <si>
+    <t>скрученной учения</t>
+  </si>
+  <si>
+    <t>скрученного учения</t>
+  </si>
+  <si>
+    <t>не вышедшем на витку</t>
+  </si>
+  <si>
+    <t>не вышедшем на виток</t>
+  </si>
+  <si>
+    <t>прстранственной устройства</t>
+  </si>
+  <si>
+    <t>простраственного устройства</t>
+  </si>
+  <si>
+    <t>многолетнего оценки</t>
+  </si>
+  <si>
+    <t>многолетней оценки</t>
+  </si>
+  <si>
+    <t>носители сведениям</t>
+  </si>
+  <si>
+    <t>носители сведений</t>
+  </si>
+  <si>
+    <t>носителями сведений</t>
+  </si>
+  <si>
+    <t>значительную значение</t>
+  </si>
+  <si>
+    <t>значительное значение</t>
+  </si>
+  <si>
+    <t>носителями сведениям</t>
+  </si>
+  <si>
+    <t>спиралевидная устройство</t>
+  </si>
+  <si>
+    <t>сриралевидное устройство</t>
+  </si>
+  <si>
+    <t>изменяя виду</t>
+  </si>
+  <si>
+    <t>изменяя вид</t>
+  </si>
+  <si>
+    <t>животно</t>
+  </si>
+  <si>
+    <t>животное</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +281,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -515,14 +658,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7256F3A-5CBA-4182-B90F-37645EE12738}">
-  <dimension ref="A2:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7265625" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -530,29 +673,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -561,25 +730,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
+  <dimension ref="A2:B19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.1796875" customWidth="1"/>
+    <col min="1" max="1" width="43.140625" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -587,7 +756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -595,7 +764,120 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F165D099-D819-4A28-902F-A04AB676CC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223F2586-AF3F-446C-A49D-D31C255523E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-570" yWindow="2355" windowWidth="18315" windowHeight="11070" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="0" yWindow="2355" windowWidth="18315" windowHeight="11070" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="195">
   <si>
     <t>исходные</t>
   </si>
@@ -229,6 +229,456 @@
   </si>
   <si>
     <t>животное</t>
+  </si>
+  <si>
+    <t>рождают отрицательная частица</t>
+  </si>
+  <si>
+    <t>рождают отрицательную частицу</t>
+  </si>
+  <si>
+    <t>устройство человека стало в один прекрасный особенность</t>
+  </si>
+  <si>
+    <t>устройство человека стало в одну прекрасную особенность</t>
+  </si>
+  <si>
+    <t>посмотреть на эту устройство</t>
+  </si>
+  <si>
+    <t>посмотреть на это устройство</t>
+  </si>
+  <si>
+    <t>сечением некой Завитка Многомерности</t>
+  </si>
+  <si>
+    <t>сечением некого Завитка Многомерности</t>
+  </si>
+  <si>
+    <t>каждый виток этой Завитка</t>
+  </si>
+  <si>
+    <t>каждый виток этого Завитка</t>
+  </si>
+  <si>
+    <t>наша общества пока является</t>
+  </si>
+  <si>
+    <t>наше общества пока является</t>
+  </si>
+  <si>
+    <t>все происхлдящее на нашей небесном теле</t>
+  </si>
+  <si>
+    <t>все происхлдящее на нашем небесном теле</t>
+  </si>
+  <si>
+    <t>называется наша Созвездие</t>
+  </si>
+  <si>
+    <t>называется наше Созвездие</t>
+  </si>
+  <si>
+    <t>но данная предположительная взгляд</t>
+  </si>
+  <si>
+    <t>но данный предположительный взгляд</t>
+  </si>
+  <si>
+    <t>в итоге действия Установки Внедрения. сложилась взгляд:</t>
+  </si>
+  <si>
+    <t>в итоге действия Установки Внедрения. сложился .взгляд:</t>
+  </si>
+  <si>
+    <t>каждая клетка входящая в живая особь</t>
+  </si>
+  <si>
+    <t>каждая клетка входящая в живую особь</t>
+  </si>
+  <si>
+    <t>привело к важнейшим нарушением в ходе</t>
+  </si>
+  <si>
+    <t>привело к важнейшим нарушениям   в ходе</t>
+  </si>
+  <si>
+    <t>однако наша общество может самостоятельно</t>
+  </si>
+  <si>
+    <t>однако наше общество может самостоятельно</t>
+  </si>
+  <si>
+    <t>из точек зрения многомерности наша земная общество</t>
+  </si>
+  <si>
+    <t>из точек зрения многомерности наше земное общество</t>
+  </si>
+  <si>
+    <t>некий площадь экстремальных случаев</t>
+  </si>
+  <si>
+    <t>некая площадь экстремальных случаев</t>
+  </si>
+  <si>
+    <t>происходящее на нашей небесном теле</t>
+  </si>
+  <si>
+    <t>происходящее на нашем небесном теле</t>
+  </si>
+  <si>
+    <t>разрушить систему изъятия нашего возможности и второй-</t>
+  </si>
+  <si>
+    <t>разрушить систему изъятия нашей возможности и второе-</t>
+  </si>
+  <si>
+    <t>есть такая расчет: Сил мне</t>
+  </si>
+  <si>
+    <t>есть такой расчет: Сил мне</t>
+  </si>
+  <si>
+    <t>Каждый  выполняет свою определенную значение</t>
+  </si>
+  <si>
+    <t>Каждый  выполняет свое определеное значение</t>
+  </si>
+  <si>
+    <t>каждая природная вид</t>
+  </si>
+  <si>
+    <t>каждый природный вид</t>
+  </si>
+  <si>
+    <t>и что самое забавное в этой случая</t>
+  </si>
+  <si>
+    <t>и что самое забавное в этом случае</t>
+  </si>
+  <si>
+    <t>попадания в их живая особь</t>
+  </si>
+  <si>
+    <t>попадания в их живую особь</t>
+  </si>
+  <si>
+    <t>на книжные прилавки  целого потока лжетайной тсточников</t>
+  </si>
+  <si>
+    <t>на книжные прилавки  целого потока лжетайных тсточников</t>
+  </si>
+  <si>
+    <t>началась всеобщая осквернение тысячелетних знаний</t>
+  </si>
+  <si>
+    <t>началось всеобщее осквернение тысячелетних знаний</t>
+  </si>
+  <si>
+    <t>Оценка этой случая приведенный в</t>
+  </si>
+  <si>
+    <t>Оценка этого  случая приведенного в</t>
+  </si>
+  <si>
+    <t>неопровержимый фактический сырье на эту вопрос</t>
+  </si>
+  <si>
+    <t>неопровержимое фактическое сырье на этот вопрос</t>
+  </si>
+  <si>
+    <t>по расчетам наша общество должна была задохнуться</t>
+  </si>
+  <si>
+    <t>по расчетам наше общество должно было задохнуться</t>
+  </si>
+  <si>
+    <t>наша небесное тело представляет собой</t>
+  </si>
+  <si>
+    <t>наше небесное тело представляет собой</t>
+  </si>
+  <si>
+    <t>самых со всей созвездия</t>
+  </si>
+  <si>
+    <t>самых со всего созвездия</t>
+  </si>
+  <si>
+    <t>в земных тюрьмах эту значение</t>
+  </si>
+  <si>
+    <t>в земных тюрьмах это значение</t>
+  </si>
+  <si>
+    <t>и охранная тревожное оповещение</t>
+  </si>
+  <si>
+    <t>и охранное тревожное оповещение</t>
+  </si>
+  <si>
+    <t>наша небесная тело была превращена</t>
+  </si>
+  <si>
+    <t>наше небесное тело было превращено</t>
+  </si>
+  <si>
+    <t>не используют свой возможность разума</t>
+  </si>
+  <si>
+    <t>не используют свою возможность разума</t>
+  </si>
+  <si>
+    <t>можно проделать в срессовых случаях</t>
+  </si>
+  <si>
+    <t>можно проделать в срессовой случаях</t>
+  </si>
+  <si>
+    <t>а некой внешней полевой устройстом</t>
+  </si>
+  <si>
+    <t>а неким внешним полевым устройстом</t>
+  </si>
+  <si>
+    <t>входящей в живая особь</t>
+  </si>
+  <si>
+    <t>входящей в живую особь</t>
+  </si>
+  <si>
+    <t>Сам это понятие</t>
+  </si>
+  <si>
+    <t>Само это понятие</t>
+  </si>
+  <si>
+    <t>по крайней мере глуп</t>
+  </si>
+  <si>
+    <t>по крайней мере глупо</t>
+  </si>
+  <si>
+    <t>что же надо сделать для налаживания больные женщины</t>
+  </si>
+  <si>
+    <t>что же надо сделать для налаживания больная женщина</t>
+  </si>
+  <si>
+    <t>необходимую для налаживания больные женщины</t>
+  </si>
+  <si>
+    <t>необходимую для налаживания больной женщины</t>
+  </si>
+  <si>
+    <t>есть весь савокупность восприятия сведений</t>
+  </si>
+  <si>
+    <t>есть вся савокупность восприятия сведений</t>
+  </si>
+  <si>
+    <t>Любая сведения из Информационных Полей должна</t>
+  </si>
+  <si>
+    <t>Любые сведения из Информационных Полей должны</t>
+  </si>
+  <si>
+    <t>Сведения многомерна</t>
+  </si>
+  <si>
+    <t>Сведения многомерны</t>
+  </si>
+  <si>
+    <t>восприятия многомерной сведениям</t>
+  </si>
+  <si>
+    <t>восприятия многомерного сведениям</t>
+  </si>
+  <si>
+    <t>для восприятия этой сведениям необходимо</t>
+  </si>
+  <si>
+    <t>для восприятия этим сведениям необходимо</t>
+  </si>
+  <si>
+    <t>при работе отделы каждый воспринимает</t>
+  </si>
+  <si>
+    <t>при работе отделов каждый воспринимает</t>
+  </si>
+  <si>
+    <t>обьъдинение мыслеобразов этой сведениям</t>
+  </si>
+  <si>
+    <t>обьъдинение мыслеобразов этим сведениям</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Небесное тело сама участвует в </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Небесное тело само участвует в </t>
+  </si>
+  <si>
+    <t>представление об энергоинформационной устройстве человека</t>
+  </si>
+  <si>
+    <t>представление об энергоинформационном устройстве человека</t>
+  </si>
+  <si>
+    <t>иногда при измения необходимость отмены казни</t>
+  </si>
+  <si>
+    <t>иногда при измении необходимости отмены казни</t>
+  </si>
+  <si>
+    <t>на наиболее целесообразную виду налаживания</t>
+  </si>
+  <si>
+    <t>на наиболее целесообразный вид налаживания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Главное итог такой изменения </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Главный итог такого изменения </t>
+  </si>
+  <si>
+    <t>посредством пространственному перемещениям</t>
+  </si>
+  <si>
+    <t>посредством пространственного перемещения</t>
+  </si>
+  <si>
+    <t>получив соответствующий свидетельство</t>
+  </si>
+  <si>
+    <t>получив соответствующее свидетельство</t>
+  </si>
+  <si>
+    <t>наша общество образует единую ноосферу</t>
+  </si>
+  <si>
+    <t>наше общество образует единую ноосферу</t>
+  </si>
+  <si>
+    <t>можно считывать любую сведения прошлого</t>
+  </si>
+  <si>
+    <t>можно считывать любые  сведения прошлого</t>
+  </si>
+  <si>
+    <t>обязательно присутствует временная местонахождение</t>
+  </si>
+  <si>
+    <t>обязательно присутствует временное местонахождение</t>
+  </si>
+  <si>
+    <t>Точно такую же значение выполняют</t>
+  </si>
+  <si>
+    <t>Точно такое же значение выполняют</t>
+  </si>
+  <si>
+    <t>Если это не однодейственная случай</t>
+  </si>
+  <si>
+    <t>Если это не однодейственный  случай</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Например  в звездоведении злая небесное тело</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Например  в звездоведении злое небесное тело</t>
+  </si>
+  <si>
+    <t>То что основная множество людей</t>
+  </si>
+  <si>
+    <t>То что основное множество людей</t>
+  </si>
+  <si>
+    <t>рассмотрим эту случай с другой стороны</t>
+  </si>
+  <si>
+    <t>рассмотрим этот случай с другой стороны</t>
+  </si>
+  <si>
+    <t>Меняя свою положение</t>
+  </si>
+  <si>
+    <t>Меняя свое положение</t>
+  </si>
+  <si>
+    <t>Подобный случай произошла и с колджовскими движениями рук</t>
+  </si>
+  <si>
+    <t>Подобный случай произошел и с колджовскими движениями рук</t>
+  </si>
+  <si>
+    <t>Если  отрицательная частица поднялся не на один</t>
+  </si>
+  <si>
+    <t>Если  отрицательная частица поднялась не на один</t>
+  </si>
+  <si>
+    <t>возможны два исхода его возврата</t>
+  </si>
+  <si>
+    <t>возможны два исхода ее возврата</t>
+  </si>
+  <si>
+    <t>возвращается на свою витку</t>
+  </si>
+  <si>
+    <t>возвращается на свой   виток</t>
+  </si>
+  <si>
+    <t>равна жизненные заряды кванта</t>
+  </si>
+  <si>
+    <t>равна жизненным зарядам кванта</t>
+  </si>
+  <si>
+    <t>возбудившего отрицательная частица</t>
+  </si>
+  <si>
+    <t>возбудившего отрицательные частицы</t>
+  </si>
+  <si>
+    <t>Это правило был использован</t>
+  </si>
+  <si>
+    <t>Это правило было использовано</t>
+  </si>
+  <si>
+    <t>неприличный движение</t>
+  </si>
+  <si>
+    <t>неприличное движение</t>
+  </si>
+  <si>
+    <t>свойства ритуальной колдовства</t>
+  </si>
+  <si>
+    <t>свойства ритуального колдовства</t>
+  </si>
+  <si>
+    <t>сущность на Земле в своей развития</t>
+  </si>
+  <si>
+    <t>сущность на Земле в своем развитии</t>
+  </si>
+  <si>
+    <t>этапе прстейшего крошечной особи</t>
+  </si>
+  <si>
+    <t>этапы прстейшей крошечной особи</t>
+  </si>
+  <si>
+    <t>Однако энергоинформационной оценка</t>
+  </si>
+  <si>
+    <t>Однако энергоинформационная оценка</t>
   </si>
 </sst>
 </file>
@@ -731,11 +1181,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:B19"/>
+  <dimension ref="A2:B94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.140625" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,6 +1326,606 @@
         <v>42</v>
       </c>
     </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>117</v>
+      </c>
+      <c r="B56" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>119</v>
+      </c>
+      <c r="B57" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>139</v>
+      </c>
+      <c r="B67" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>141</v>
+      </c>
+      <c r="B68" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>147</v>
+      </c>
+      <c r="B71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>149</v>
+      </c>
+      <c r="B72" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>151</v>
+      </c>
+      <c r="B73" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>159</v>
+      </c>
+      <c r="B77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+      <c r="B78" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>169</v>
+      </c>
+      <c r="B82" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>173</v>
+      </c>
+      <c r="B84" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>175</v>
+      </c>
+      <c r="B85" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>177</v>
+      </c>
+      <c r="B86" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>179</v>
+      </c>
+      <c r="B87" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>181</v>
+      </c>
+      <c r="B88" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>183</v>
+      </c>
+      <c r="B89" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>185</v>
+      </c>
+      <c r="B90" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>187</v>
+      </c>
+      <c r="B91" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>189</v>
+      </c>
+      <c r="B92" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>191</v>
+      </c>
+      <c r="B93" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>193</v>
+      </c>
+      <c r="B94" t="s">
+        <v>194</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB185A50-94DD-45B5-8FF8-DFF190E84E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0E0F05-182E-473D-AA92-0AB8961FE025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="600" yWindow="1365" windowWidth="18315" windowHeight="11520" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
   <si>
     <t>исходные</t>
   </si>
@@ -301,6 +301,144 @@
   </si>
   <si>
     <t xml:space="preserve">романа </t>
+  </si>
+  <si>
+    <t>тем самым занижает свой возможности разума</t>
+  </si>
+  <si>
+    <t>тем самым занижает свои возможности разума</t>
+  </si>
+  <si>
+    <t>богословно-управленческий заведение эту толкование</t>
+  </si>
+  <si>
+    <t>богословно-управленческое заведение это толкование</t>
+  </si>
+  <si>
+    <t>последователи этого обособленного закрытого вероучения</t>
+  </si>
+  <si>
+    <t>последователи этой обособленные закрытые вероучения</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Чтобы произошла воплощение вашей мыслеобраза</t>
+  </si>
+  <si>
+    <t>Чтобы произошло воплощение вашего мыслеобраза</t>
+  </si>
+  <si>
+    <t>это основа высшей колдовства</t>
+  </si>
+  <si>
+    <t>это основа высшего колдовства</t>
+  </si>
+  <si>
+    <t>общего научного савокупности миропонимания</t>
+  </si>
+  <si>
+    <t>общей научной савокупности миропонимания</t>
+  </si>
+  <si>
+    <t>это папка можно получить многомерную чертеж-рисунок</t>
+  </si>
+  <si>
+    <t>этой папкой можно получить многомерный чертеж-рисунок</t>
+  </si>
+  <si>
+    <t>этот последствие был великолепноопытно доказан академиком</t>
+  </si>
+  <si>
+    <t>это последствие было  великолепноопытно доказано  академиком</t>
+  </si>
+  <si>
+    <t>важное положение существование большой скрытого вещества</t>
+  </si>
+  <si>
+    <t>важное положение существование большого скрытого вещества</t>
+  </si>
+  <si>
+    <t>смертельный для любой общества</t>
+  </si>
+  <si>
+    <t>смертельный для любого общества</t>
+  </si>
+  <si>
+    <t>запасенный жизненный щаряд вращение скрученного</t>
+  </si>
+  <si>
+    <t>запасенный жизненный заряд вращение скрученного</t>
+  </si>
+  <si>
+    <t>изменяющее спиновую положение неделимых частиц</t>
+  </si>
+  <si>
+    <t>изменяющее спиновое положение неделимых частиц</t>
+  </si>
+  <si>
+    <t>ДНК представляет собой двойную завиток</t>
+  </si>
+  <si>
+    <t>ДНК представляет собой двойной завиток</t>
+  </si>
+  <si>
+    <t>Земля выгдядит количественный завитком напоминающей пружину</t>
+  </si>
+  <si>
+    <t>Земля выгдядит количественным завитком напоминающим пружину</t>
+  </si>
+  <si>
+    <t>Животно это используется в брачных танцах</t>
+  </si>
+  <si>
+    <t>Животным это используется в брачных танцах</t>
+  </si>
+  <si>
+    <t>Мыслящего Океана покрывавшего небесому телу</t>
+  </si>
+  <si>
+    <t>Мыслящего Океана покрывавшего небесое тело</t>
+  </si>
+  <si>
+    <t>Вода является двухмерной отображением рычага</t>
+  </si>
+  <si>
+    <t>Вода является двухмерным отображением рычага</t>
+  </si>
+  <si>
+    <t>хранит внушительный количество сведениям</t>
+  </si>
+  <si>
+    <t>хранит внушительное количество сведенй</t>
+  </si>
+  <si>
+    <t>наступают связующие случая</t>
+  </si>
+  <si>
+    <t>наступают связующие случаи</t>
+  </si>
+  <si>
+    <t>сведения может быть записана</t>
+  </si>
+  <si>
+    <t>сведения могут быть записаны</t>
+  </si>
+  <si>
+    <t>молекулярное устройство углерода</t>
+  </si>
+  <si>
+    <t>молекулярную устройства углерода</t>
+  </si>
+  <si>
+    <t>как "считывается" сведения</t>
+  </si>
+  <si>
+    <t>как "считываются" сведения</t>
+  </si>
+  <si>
+    <t>тонкие руки и ножи</t>
+  </si>
+  <si>
+    <t>тонкие руки и ноги</t>
   </si>
 </sst>
 </file>
@@ -387,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -396,6 +534,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1063,11 +1202,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:B10"/>
+  <dimension ref="A2:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.5703125" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="1" max="1" width="59.85546875" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1133,8 +1272,193 @@
         <v>26</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0E0F05-182E-473D-AA92-0AB8961FE025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524BC794-6780-4127-8F70-E9B240DBD70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="1365" windowWidth="18315" windowHeight="11520" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -33,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="106">
   <si>
     <t>исходные</t>
   </si>
@@ -114,12 +111,6 @@
     <t>спиновое</t>
   </si>
   <si>
-    <t>скрученой звездоведения</t>
-  </si>
-  <si>
-    <t>скрученного звездоведения</t>
-  </si>
-  <si>
     <t>животно</t>
   </si>
   <si>
@@ -303,66 +294,6 @@
     <t xml:space="preserve">романа </t>
   </si>
   <si>
-    <t>тем самым занижает свой возможности разума</t>
-  </si>
-  <si>
-    <t>тем самым занижает свои возможности разума</t>
-  </si>
-  <si>
-    <t>богословно-управленческий заведение эту толкование</t>
-  </si>
-  <si>
-    <t>богословно-управленческое заведение это толкование</t>
-  </si>
-  <si>
-    <t>последователи этого обособленного закрытого вероучения</t>
-  </si>
-  <si>
-    <t>последователи этой обособленные закрытые вероучения</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Чтобы произошла воплощение вашей мыслеобраза</t>
-  </si>
-  <si>
-    <t>Чтобы произошло воплощение вашего мыслеобраза</t>
-  </si>
-  <si>
-    <t>это основа высшей колдовства</t>
-  </si>
-  <si>
-    <t>это основа высшего колдовства</t>
-  </si>
-  <si>
-    <t>общего научного савокупности миропонимания</t>
-  </si>
-  <si>
-    <t>общей научной савокупности миропонимания</t>
-  </si>
-  <si>
-    <t>это папка можно получить многомерную чертеж-рисунок</t>
-  </si>
-  <si>
-    <t>этой папкой можно получить многомерный чертеж-рисунок</t>
-  </si>
-  <si>
-    <t>этот последствие был великолепноопытно доказан академиком</t>
-  </si>
-  <si>
-    <t>это последствие было  великолепноопытно доказано  академиком</t>
-  </si>
-  <si>
-    <t>важное положение существование большой скрытого вещества</t>
-  </si>
-  <si>
-    <t>важное положение существование большого скрытого вещества</t>
-  </si>
-  <si>
-    <t>смертельный для любой общества</t>
-  </si>
-  <si>
-    <t>смертельный для любого общества</t>
-  </si>
-  <si>
     <t>запасенный жизненный щаряд вращение скрученного</t>
   </si>
   <si>
@@ -439,6 +370,12 @@
   </si>
   <si>
     <t>тонкие руки и ноги</t>
+  </si>
+  <si>
+    <t>не нашёл</t>
+  </si>
+  <si>
+    <t>листовку,</t>
   </si>
 </sst>
 </file>
@@ -493,7 +430,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,6 +449,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -525,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -535,6 +478,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -869,14 +813,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7256F3A-5CBA-4182-B90F-37645EE12738}">
-  <dimension ref="A2:B63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:B64"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="1" max="1" width="35.7265625" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -884,42 +828,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -927,272 +871,277 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>79</v>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1202,24 +1151,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:B34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:C23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="59.85546875" customWidth="1"/>
+    <col min="1" max="1" width="59.81640625" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="3" width="25.08984375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1227,7 +1177,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1235,44 +1185,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -1280,7 +1233,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -1288,15 +1241,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
         <v>85</v>
       </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -1304,7 +1257,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -1312,15 +1265,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1328,7 +1281,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -1336,7 +1289,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -1344,15 +1297,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
         <v>98</v>
       </c>
-      <c r="B21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>100</v>
       </c>
@@ -1360,100 +1313,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>102</v>
       </c>
       <c r="B23" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>114</v>
-      </c>
-      <c r="B29" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>121</v>
-      </c>
-      <c r="B32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1465,11 +1330,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04419A4-ABD5-463C-A44D-E18099D3F2F0}">
   <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524BC794-6780-4127-8F70-E9B240DBD70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0E0F05-182E-473D-AA92-0AB8961FE025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="600" yWindow="1365" windowWidth="18315" windowHeight="11520" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
   <si>
     <t>исходные</t>
   </si>
@@ -111,6 +114,12 @@
     <t>спиновое</t>
   </si>
   <si>
+    <t>скрученой звездоведения</t>
+  </si>
+  <si>
+    <t>скрученного звездоведения</t>
+  </si>
+  <si>
     <t>животно</t>
   </si>
   <si>
@@ -294,6 +303,66 @@
     <t xml:space="preserve">романа </t>
   </si>
   <si>
+    <t>тем самым занижает свой возможности разума</t>
+  </si>
+  <si>
+    <t>тем самым занижает свои возможности разума</t>
+  </si>
+  <si>
+    <t>богословно-управленческий заведение эту толкование</t>
+  </si>
+  <si>
+    <t>богословно-управленческое заведение это толкование</t>
+  </si>
+  <si>
+    <t>последователи этого обособленного закрытого вероучения</t>
+  </si>
+  <si>
+    <t>последователи этой обособленные закрытые вероучения</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Чтобы произошла воплощение вашей мыслеобраза</t>
+  </si>
+  <si>
+    <t>Чтобы произошло воплощение вашего мыслеобраза</t>
+  </si>
+  <si>
+    <t>это основа высшей колдовства</t>
+  </si>
+  <si>
+    <t>это основа высшего колдовства</t>
+  </si>
+  <si>
+    <t>общего научного савокупности миропонимания</t>
+  </si>
+  <si>
+    <t>общей научной савокупности миропонимания</t>
+  </si>
+  <si>
+    <t>это папка можно получить многомерную чертеж-рисунок</t>
+  </si>
+  <si>
+    <t>этой папкой можно получить многомерный чертеж-рисунок</t>
+  </si>
+  <si>
+    <t>этот последствие был великолепноопытно доказан академиком</t>
+  </si>
+  <si>
+    <t>это последствие было  великолепноопытно доказано  академиком</t>
+  </si>
+  <si>
+    <t>важное положение существование большой скрытого вещества</t>
+  </si>
+  <si>
+    <t>важное положение существование большого скрытого вещества</t>
+  </si>
+  <si>
+    <t>смертельный для любой общества</t>
+  </si>
+  <si>
+    <t>смертельный для любого общества</t>
+  </si>
+  <si>
     <t>запасенный жизненный щаряд вращение скрученного</t>
   </si>
   <si>
@@ -370,12 +439,6 @@
   </si>
   <si>
     <t>тонкие руки и ноги</t>
-  </si>
-  <si>
-    <t>не нашёл</t>
-  </si>
-  <si>
-    <t>листовку,</t>
   </si>
 </sst>
 </file>
@@ -430,7 +493,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,12 +512,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -468,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -478,7 +535,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -813,14 +869,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7256F3A-5CBA-4182-B90F-37645EE12738}">
-  <dimension ref="A2:B64"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:B63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7265625" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -828,42 +884,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -871,277 +927,272 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1151,25 +1202,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:C23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:B34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.81640625" customWidth="1"/>
+    <col min="1" max="1" width="59.85546875" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
-    <col min="3" max="3" width="25.08984375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1177,7 +1227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1185,47 +1235,44 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -1233,7 +1280,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -1241,15 +1288,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
         <v>84</v>
       </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -1257,7 +1304,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -1265,15 +1312,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>90</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1281,7 +1328,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -1289,7 +1336,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -1297,15 +1344,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
         <v>99</v>
       </c>
-      <c r="B21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>100</v>
       </c>
@@ -1313,12 +1360,100 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>102</v>
       </c>
       <c r="B23" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1330,11 +1465,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04419A4-ABD5-463C-A44D-E18099D3F2F0}">
   <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0E0F05-182E-473D-AA92-0AB8961FE025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDF78AB-34C9-4D32-AB8F-0D0C4A975145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="1365" windowWidth="18315" windowHeight="11520" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="675" yWindow="975" windowWidth="18315" windowHeight="11520" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="469">
   <si>
     <t>исходные</t>
   </si>
@@ -439,6 +439,1035 @@
   </si>
   <si>
     <t>тонкие руки и ноги</t>
+  </si>
+  <si>
+    <t>очередная обьединение общества</t>
+  </si>
+  <si>
+    <t>очередное обьединение общества</t>
+  </si>
+  <si>
+    <t>по воле чуждого земной развития злого разума</t>
+  </si>
+  <si>
+    <t>по воле чуждому земному развитию злого разума</t>
+  </si>
+  <si>
+    <t>последствие известен давно</t>
+  </si>
+  <si>
+    <t>последствие известно давно</t>
+  </si>
+  <si>
+    <t>А "марсианский метеорит" полностью добил эту учение</t>
+  </si>
+  <si>
+    <t>А "марсианский метеорит" полностью добил это учение</t>
+  </si>
+  <si>
+    <t>На первый взгляд жуткий истребление народа</t>
+  </si>
+  <si>
+    <t>На первый взгляд жуткое истребление народа</t>
+  </si>
+  <si>
+    <t>способности к парения в воздухе</t>
+  </si>
+  <si>
+    <t>способности к парению в воздухе</t>
+  </si>
+  <si>
+    <t>по 10 сложилась случай воплощения</t>
+  </si>
+  <si>
+    <t>по 10 сложился случай воплощения</t>
+  </si>
+  <si>
+    <t>Случай коренным образом изменился при рассмотрении</t>
+  </si>
+  <si>
+    <t>Случай коренным образом изменилась при рассмотрении</t>
+  </si>
+  <si>
+    <t>один из парламентариев в беседа</t>
+  </si>
+  <si>
+    <t>один из парламентариев в беседе</t>
+  </si>
+  <si>
+    <t>после любой даже незначительный увечья</t>
+  </si>
+  <si>
+    <t>после любого даже незначительного увечья</t>
+  </si>
+  <si>
+    <t>удалось заразить минингитоподобным заразой</t>
+  </si>
+  <si>
+    <t>удалось заразить минингитоподобной заразой</t>
+  </si>
+  <si>
+    <t>внедрение энергоинформационного зараза</t>
+  </si>
+  <si>
+    <t>внедрение энергоинформационной заразы</t>
+  </si>
+  <si>
+    <t>и эта зараза дал намеченые плоды</t>
+  </si>
+  <si>
+    <t>и эта зараза дала намеченые плоды</t>
+  </si>
+  <si>
+    <t>паталогия в развития землян</t>
+  </si>
+  <si>
+    <t>паталогия в развитии землян</t>
+  </si>
+  <si>
+    <t>протекающий по завитка</t>
+  </si>
+  <si>
+    <t>протекающий по завиткам</t>
+  </si>
+  <si>
+    <t>наше небесное тело было превращено в некое жертвенное посевное поле</t>
+  </si>
+  <si>
+    <t>наше небесное тело была превращена в некую жертвенную посевное поле</t>
+  </si>
+  <si>
+    <t>любые сведения из Несущих сведения Полей должна восприниматься</t>
+  </si>
+  <si>
+    <t>любые сведения из Несущих сведений Полей должны восприниматься</t>
+  </si>
+  <si>
+    <t>неизбежно часть сведениям теряется</t>
+  </si>
+  <si>
+    <t>неизбежно часть сведениий теряется</t>
+  </si>
+  <si>
+    <t>об энергоинформационной устройстве человека</t>
+  </si>
+  <si>
+    <t>об энергоинформационном устройстве человека</t>
+  </si>
+  <si>
+    <t>При этом образуется количественная устройство напоминающая</t>
+  </si>
+  <si>
+    <t>При этом образуется количественное  устройство напоминаящее</t>
+  </si>
+  <si>
+    <t>наша существующая живая особь</t>
+  </si>
+  <si>
+    <t>наш существующий живая особь</t>
+  </si>
+  <si>
+    <t>точную самоповтор исходного живой особи</t>
+  </si>
+  <si>
+    <t>точный самоповтор исходной живой особи</t>
+  </si>
+  <si>
+    <t>происходит  разрушение внутренней устройства</t>
+  </si>
+  <si>
+    <t>происходит  разрушение внутреннего устройства</t>
+  </si>
+  <si>
+    <t>тайноведов прошлого и настоящего позволил сделать</t>
+  </si>
+  <si>
+    <t>тайноведов прошлого и настоящего позволило сделать</t>
+  </si>
+  <si>
+    <t>ожидает весьма неприятная случай</t>
+  </si>
+  <si>
+    <t>ожидает весьма неприятный случай</t>
+  </si>
+  <si>
+    <t>выполлняют основную значение</t>
+  </si>
+  <si>
+    <t>выполлняют основное значение</t>
+  </si>
+  <si>
+    <t>антиподом росийского народности</t>
+  </si>
+  <si>
+    <t>антиподом росийской народности</t>
+  </si>
+  <si>
+    <t>нуждаются в притоке нового возможности</t>
+  </si>
+  <si>
+    <t>нуждаются в притоке новоой возможности</t>
+  </si>
+  <si>
+    <t>политичекий и экономический возможность</t>
+  </si>
+  <si>
+    <t>политичекую и экономическую возможность</t>
+  </si>
+  <si>
+    <t>за последнее время земной обществом</t>
+  </si>
+  <si>
+    <t>за последнее время земным обществом</t>
+  </si>
+  <si>
+    <t>такой правило работы просто вынуждал</t>
+  </si>
+  <si>
+    <t>такой правило работы просто вынуждало</t>
+  </si>
+  <si>
+    <t>есть какая то щелчка, действующая на погибель</t>
+  </si>
+  <si>
+    <t>есть какой то щелчок, действующий на погибель</t>
+  </si>
+  <si>
+    <t>свою отведенную значение</t>
+  </si>
+  <si>
+    <t>свое отведенное значение</t>
+  </si>
+  <si>
+    <t>нельзя было дать российскому народу</t>
+  </si>
+  <si>
+    <t>нельзя было дать российскому народности</t>
+  </si>
+  <si>
+    <t>символом древнейшей испанской колдовства</t>
+  </si>
+  <si>
+    <t>символом древнейшего испанского колдовства</t>
+  </si>
+  <si>
+    <t>ПечатьСША в своей обозначении</t>
+  </si>
+  <si>
+    <t>ПечатьСША в своем обозначении</t>
+  </si>
+  <si>
+    <t>нужна и непосредственная обряд</t>
+  </si>
+  <si>
+    <t>нужнен и непосредственный обряд</t>
+  </si>
+  <si>
+    <t>во время своего встрече в Англию</t>
+  </si>
+  <si>
+    <t>во время своей  встречи в Англии</t>
+  </si>
+  <si>
+    <t>всемирный тайный  семья, руководимый</t>
+  </si>
+  <si>
+    <t>всемирная тайная  семья, руководимая</t>
+  </si>
+  <si>
+    <t>в своих воплощениях проходит следующее этапе  развития</t>
+  </si>
+  <si>
+    <t>в своих воплощениях проходит следующие этапы  развития</t>
+  </si>
+  <si>
+    <t>весь выдающий многомерный живая особь</t>
+  </si>
+  <si>
+    <t>вся выдающаяся многомерная живая особь</t>
+  </si>
+  <si>
+    <t>полнлстью противоречат ходе мыслей</t>
+  </si>
+  <si>
+    <t>полнлстью противоречат ходу мыслей</t>
+  </si>
+  <si>
+    <t>организовавшему такую случай</t>
+  </si>
+  <si>
+    <t>организовавшему такой случай</t>
+  </si>
+  <si>
+    <t>вся изменения прошла</t>
+  </si>
+  <si>
+    <t>все изменения прошли</t>
+  </si>
+  <si>
+    <t>у сына после той изменения</t>
+  </si>
+  <si>
+    <t>у сына после того изменения</t>
+  </si>
+  <si>
+    <t>два года назад могла за считанные минуты пройти</t>
+  </si>
+  <si>
+    <t>два года назад могло за считанные минуты пройти</t>
+  </si>
+  <si>
+    <t>как же прошла изменение в данном случае с мальчиком</t>
+  </si>
+  <si>
+    <t>как же прошло изменение в данном случае с мальчиком</t>
+  </si>
+  <si>
+    <t>обнаружили сильнейший напряжение</t>
+  </si>
+  <si>
+    <t>обнаружили сильнейшее напряжение</t>
+  </si>
+  <si>
+    <t>время изменения позволил выявить следующее</t>
+  </si>
+  <si>
+    <t>время изменения позволило выявить следующее</t>
+  </si>
+  <si>
+    <t>для того чтобы мыслеобраз  получалась работоспособной</t>
+  </si>
+  <si>
+    <t>для того чтобы мыслеобраз  получалался работоспособным</t>
+  </si>
+  <si>
+    <t>к снижению  энергетической возможности человека</t>
+  </si>
+  <si>
+    <t>к снижению  энергетического возможности человека</t>
+  </si>
+  <si>
+    <t>хранитель тайноведения или тайный семья</t>
+  </si>
+  <si>
+    <t>хранитель тайноведения или тайная семья</t>
+  </si>
+  <si>
+    <t>злая небесное тело Сатурн</t>
+  </si>
+  <si>
+    <t>злое небесное тело Сатурн</t>
+  </si>
+  <si>
+    <t>вспомните вот такой проверочный случай</t>
+  </si>
+  <si>
+    <t>вспомните вот такую проверочный случай</t>
+  </si>
+  <si>
+    <t>так бы увидел эту изображению ясновидящий</t>
+  </si>
+  <si>
+    <t>так бы увидел это изображение ясновидящий</t>
+  </si>
+  <si>
+    <t>замысел жертвы на восковую образу</t>
+  </si>
+  <si>
+    <t>замысел жертвы на восковой образ</t>
+  </si>
+  <si>
+    <t>рядом количественного скачка</t>
+  </si>
+  <si>
+    <t>рядом количественный скачок</t>
+  </si>
+  <si>
+    <t>Эти случая воспроизводятся</t>
+  </si>
+  <si>
+    <t>Эти случаи воспроизводятся</t>
+  </si>
+  <si>
+    <t>проверочная случай в автобусе произошла</t>
+  </si>
+  <si>
+    <t>проверочный случай в автобусе произошел</t>
+  </si>
+  <si>
+    <t>на восковую образу</t>
+  </si>
+  <si>
+    <t>на восковой образ</t>
+  </si>
+  <si>
+    <t>поднимается на более высокую виток</t>
+  </si>
+  <si>
+    <t>поднимается на более высокий виток</t>
+  </si>
+  <si>
+    <t>на этой "запрещенной"витке</t>
+  </si>
+  <si>
+    <t>на этом "запрещенном"витке</t>
+  </si>
+  <si>
+    <t>С каждой временным промежутком</t>
+  </si>
+  <si>
+    <t>С каждым временным промежутком</t>
+  </si>
+  <si>
+    <t>Круглая его образ</t>
+  </si>
+  <si>
+    <t>Круглый его образ</t>
+  </si>
+  <si>
+    <t>Когда сложенная заряд излучения</t>
+  </si>
+  <si>
+    <t>Когда сложенный заряд излучения</t>
+  </si>
+  <si>
+    <t>При показания этого движения рук</t>
+  </si>
+  <si>
+    <t>При показании этого движения рук</t>
+  </si>
+  <si>
+    <t>В науки о нло давно известно</t>
+  </si>
+  <si>
+    <t>В науке о нло давно известно</t>
+  </si>
+  <si>
+    <t>Ведь при подобной разведении руками</t>
+  </si>
+  <si>
+    <t>Ведь при подобном разведении руками</t>
+  </si>
+  <si>
+    <t>Непонимание законов потусторонней колдовства</t>
+  </si>
+  <si>
+    <t>Непонимание законов потустороннего колдовства</t>
+  </si>
+  <si>
+    <t>Для этой нехитрой действия</t>
+  </si>
+  <si>
+    <t>Для этого нехитрого действия</t>
+  </si>
+  <si>
+    <t>применяются в разрушающего колдовства</t>
+  </si>
+  <si>
+    <t>применяются в разрушающем колдовстве</t>
+  </si>
+  <si>
+    <t>будем от эниологического учения переходить к применению</t>
+  </si>
+  <si>
+    <t>будем от эниологической учения переходить к применении</t>
+  </si>
+  <si>
+    <t>Как и  в словесного колдовства</t>
+  </si>
+  <si>
+    <t>Как и  в словесном колдовстве</t>
+  </si>
+  <si>
+    <t>и не хватает многих ключ</t>
+  </si>
+  <si>
+    <t>и не хватает многих ключей</t>
+  </si>
+  <si>
+    <t>возрастает возможность потери заряды</t>
+  </si>
+  <si>
+    <t>возрастает возможность потери зарядов</t>
+  </si>
+  <si>
+    <t>за сведения ,полученную через обряды</t>
+  </si>
+  <si>
+    <t>за сведения ,полученные через обряды</t>
+  </si>
+  <si>
+    <t>энергоинформацоионный оценка любых видов</t>
+  </si>
+  <si>
+    <t>энергоинформацоионная оценка любых видов</t>
+  </si>
+  <si>
+    <t>одет в утепленную военную образу</t>
+  </si>
+  <si>
+    <t>одет в утепленный военный образ</t>
+  </si>
+  <si>
+    <t>объединяются в семью, не в тот особенность</t>
+  </si>
+  <si>
+    <t>объединяются в семью, не в том особенность</t>
+  </si>
+  <si>
+    <t>С этого особенности в Несущих сведения Полях</t>
+  </si>
+  <si>
+    <t>С этой особенности в Несущих сведениях  Полях</t>
+  </si>
+  <si>
+    <t>В тот особенность когда Николай</t>
+  </si>
+  <si>
+    <t>В эту особенность когда Николай</t>
+  </si>
+  <si>
+    <t>в ИП остается ваш местоположение нападения</t>
+  </si>
+  <si>
+    <t>в ИП остается ваше местоположение нападения</t>
+  </si>
+  <si>
+    <t>Это было ответным предложением мощнейшей волшебной семьи</t>
+  </si>
+  <si>
+    <t>Это была ответная предложения мощнейшая волшебного семьи</t>
+  </si>
+  <si>
+    <t>Поэтому индийский колдовской семья был вынужден</t>
+  </si>
+  <si>
+    <t>Поэтому индийская колдовская семья была вынуждена</t>
+  </si>
+  <si>
+    <t>при этом прихватить ваш возможность</t>
+  </si>
+  <si>
+    <t>при этом прихватить вашу возможность</t>
+  </si>
+  <si>
+    <t>За какую приказ вы болеете</t>
+  </si>
+  <si>
+    <t>За какой приказ вы болеете</t>
+  </si>
+  <si>
+    <t>строго определенный местоположение в Несущих</t>
+  </si>
+  <si>
+    <t>строго определенное местоположение в Несущих</t>
+  </si>
+  <si>
+    <t>перехода к рыночной рапределении</t>
+  </si>
+  <si>
+    <t>перехода к рыночному рапределению</t>
+  </si>
+  <si>
+    <t>существует и более тонкий особенность правила</t>
+  </si>
+  <si>
+    <t>существует и более тонкая особенность правил</t>
+  </si>
+  <si>
+    <t>касается не только определенной эниологической применения</t>
+  </si>
+  <si>
+    <t>касается не только определенного эниологического применения</t>
+  </si>
+  <si>
+    <t>замысел "подсунул" очередную проверочный случай</t>
+  </si>
+  <si>
+    <t>замысел "подсунул" очередной проверочный случай</t>
+  </si>
+  <si>
+    <t>занятии была раскрыта какая-то вопрос</t>
+  </si>
+  <si>
+    <t>занятии был раскрыт какой-то вопрос</t>
+  </si>
+  <si>
+    <t>приступить к следующей вопросе</t>
+  </si>
+  <si>
+    <t>приступить к следующему вопросу</t>
+  </si>
+  <si>
+    <t>Следующий проверочный случай</t>
+  </si>
+  <si>
+    <t>Следующая проверочная случай</t>
+  </si>
+  <si>
+    <t>статья на нужную вопрос</t>
+  </si>
+  <si>
+    <t>статья на нужный вопрос</t>
+  </si>
+  <si>
+    <t>необязательно в той образе</t>
+  </si>
+  <si>
+    <t>необязательно в том образе</t>
+  </si>
+  <si>
+    <t>пока это глупейшая случай существует</t>
+  </si>
+  <si>
+    <t>пока этот глупейший случай существует</t>
+  </si>
+  <si>
+    <t>является служба в вооруженные силы</t>
+  </si>
+  <si>
+    <t>является служба в вооруженных силах</t>
+  </si>
+  <si>
+    <t>этапе энергоинформационой изменения</t>
+  </si>
+  <si>
+    <t>этапе энергоинформационого изменения</t>
+  </si>
+  <si>
+    <t>повысить свой энергоинформационной возможность</t>
+  </si>
+  <si>
+    <t>повысить свою энергоинформационную возможность</t>
+  </si>
+  <si>
+    <t>эта вопрос будет подробно рассмотрена</t>
+  </si>
+  <si>
+    <t>этот вопрос будет подробно рассмотрен</t>
+  </si>
+  <si>
+    <t>кроме рецептов трехмерной  природной  колдовства</t>
+  </si>
+  <si>
+    <t>кроме рецептов трехмерного природного  колдовства</t>
+  </si>
+  <si>
+    <t>любую бумажное издание</t>
+  </si>
+  <si>
+    <t>любое бумажное издание</t>
+  </si>
+  <si>
+    <t>взять всю необходимую сведения</t>
+  </si>
+  <si>
+    <t>взять все необходимые сведения</t>
+  </si>
+  <si>
+    <t>верните изъятый возможность</t>
+  </si>
+  <si>
+    <t>верните изъятую возможность</t>
+  </si>
+  <si>
+    <t>именно зтот особенность обязательно</t>
+  </si>
+  <si>
+    <t>именно зта особенность обязательно</t>
+  </si>
+  <si>
+    <t>в основной множества школ</t>
+  </si>
+  <si>
+    <t>в основном множестве школ</t>
+  </si>
+  <si>
+    <t>тот колдовской совместное сознание</t>
+  </si>
+  <si>
+    <t>то колдовское совместное сознание</t>
+  </si>
+  <si>
+    <t>вернуть изъятый возможность</t>
+  </si>
+  <si>
+    <t>вернуть изъятую возможность</t>
+  </si>
+  <si>
+    <t>в итоге   проводимой изменения</t>
+  </si>
+  <si>
+    <t>в итоге   проводимого изменения</t>
+  </si>
+  <si>
+    <t>такую изображению</t>
+  </si>
+  <si>
+    <t>такое изображение</t>
+  </si>
+  <si>
+    <t>выделяется "чистая заряд"которая идет</t>
+  </si>
+  <si>
+    <t>выделяется "чистый заряд"который идет</t>
+  </si>
+  <si>
+    <t>идет на увкличение информационного возможности целительницы</t>
+  </si>
+  <si>
+    <t>идет на увкличение информационной возможности целительницы</t>
+  </si>
+  <si>
+    <t>в некий  энергоинформационный "хранилище"</t>
+  </si>
+  <si>
+    <t>в некое  энергоинформационное "хранилище"</t>
+  </si>
+  <si>
+    <t>в полной налаживания энергоинформационного обмена</t>
+  </si>
+  <si>
+    <t>в полном налаживании энергоинформационного обмена</t>
+  </si>
+  <si>
+    <t>совершено разная ответ</t>
+  </si>
+  <si>
+    <t>совершено разный ответ</t>
+  </si>
+  <si>
+    <t>язык общения по свой устройстве</t>
+  </si>
+  <si>
+    <t>язык общения по своему устройству</t>
+  </si>
+  <si>
+    <t>при помощи коротых общается данный народность</t>
+  </si>
+  <si>
+    <t>при помощи коротых общается данная народность</t>
+  </si>
+  <si>
+    <t>значения мата в развития росийского народности</t>
+  </si>
+  <si>
+    <t>значения мата в развитии росийской народности</t>
+  </si>
+  <si>
+    <t>верят исконной целительстве</t>
+  </si>
+  <si>
+    <t>верят исконному целительству</t>
+  </si>
+  <si>
+    <t>церковная колдовство позволяет</t>
+  </si>
+  <si>
+    <t>церковное колдовство позволяет</t>
+  </si>
+  <si>
+    <t>оставивших в ИП  свой местопожение  проклятий</t>
+  </si>
+  <si>
+    <t>оставивших в ИП  свое местопожение  проклятий</t>
+  </si>
+  <si>
+    <t>в основу способа нейролингвистического установки</t>
+  </si>
+  <si>
+    <t>в основу способа нейролингвистической установки</t>
+  </si>
+  <si>
+    <t>выглядел ход энергоинформационной изменения</t>
+  </si>
+  <si>
+    <t>выглядел ход энергоинформационного изменения</t>
+  </si>
+  <si>
+    <t>живой разумный  потусторонне-мыслительный живая особь</t>
+  </si>
+  <si>
+    <t>живую разумную  потусторонне-мыслительную живую особь</t>
+  </si>
+  <si>
+    <t>саморазвивающийся порабощающий разумный  живая особь</t>
+  </si>
+  <si>
+    <t>саморазвивающася порабощающая разумная  живая особь</t>
+  </si>
+  <si>
+    <t>высвобождение неиспользованного возможности</t>
+  </si>
+  <si>
+    <t>высвобождение неиспользованной возможности</t>
+  </si>
+  <si>
+    <t>Этой  вопросе посвящен раздел</t>
+  </si>
+  <si>
+    <t>Этому  вопросу посвящен раздел</t>
+  </si>
+  <si>
+    <t>Причем этой вопросе</t>
+  </si>
+  <si>
+    <t>Причем этому вопросу</t>
+  </si>
+  <si>
+    <t>не было посвящено ни одной обнародования</t>
+  </si>
+  <si>
+    <t>не было посвящено ни одного обнародования</t>
+  </si>
+  <si>
+    <t>у одной больные женщины просматривался сильнейший</t>
+  </si>
+  <si>
+    <t>у одной больной женщины просматривался сильнейшее</t>
+  </si>
+  <si>
+    <t>В армянской колдовства для снятия порчи</t>
+  </si>
+  <si>
+    <t>В армянском колдовстве для снятия порчи</t>
+  </si>
+  <si>
+    <t>человек попадает в важнейшую случай</t>
+  </si>
+  <si>
+    <t>человек попадает в важный случай</t>
+  </si>
+  <si>
+    <t>в итоге крупной увечья</t>
+  </si>
+  <si>
+    <t>в итоге крупных увечий</t>
+  </si>
+  <si>
+    <t>У больные женщины при эникоррекции</t>
+  </si>
+  <si>
+    <t>У больной женщины при эникоррекции</t>
+  </si>
+  <si>
+    <t>был обнаружен сильнейший перенапряжение</t>
+  </si>
+  <si>
+    <t>был обнаружено сильнейшее перенапряжение</t>
+  </si>
+  <si>
+    <t>связанный с похоронами</t>
+  </si>
+  <si>
+    <t>связанное с похоронами</t>
+  </si>
+  <si>
+    <t>сильнейшей черепно-мозговой  увечья</t>
+  </si>
+  <si>
+    <t>сильнейшего черепно-мозгового  увечья</t>
+  </si>
+  <si>
+    <t>Этой вопросе посвящено</t>
+  </si>
+  <si>
+    <t>Этому вопросу посвящено</t>
+  </si>
+  <si>
+    <t>рассмотреть сам особенность</t>
+  </si>
+  <si>
+    <t>рассмотреть саму особенность</t>
+  </si>
+  <si>
+    <t>на европейской земли в основном</t>
+  </si>
+  <si>
+    <t>на европейской земле в основном</t>
+  </si>
+  <si>
+    <t>повторно сменяемый средство</t>
+  </si>
+  <si>
+    <t>повторно сменяемое средство</t>
+  </si>
+  <si>
+    <t>многолетний оценка причин</t>
+  </si>
+  <si>
+    <t>многолетняя оценка причин</t>
+  </si>
+  <si>
+    <t>иных заболеваний показал</t>
+  </si>
+  <si>
+    <t>иных заболеваний показала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">любая увечье </t>
+  </si>
+  <si>
+    <t xml:space="preserve">любое увечье </t>
+  </si>
+  <si>
+    <t>нашей Созвездия</t>
+  </si>
+  <si>
+    <t>нашего Созвездия</t>
+  </si>
+  <si>
+    <t>обстановкой того или иного области</t>
+  </si>
+  <si>
+    <t>обстановкой тогй или иной области</t>
+  </si>
+  <si>
+    <t>дали очень увлекательную подсчету</t>
+  </si>
+  <si>
+    <t>дали очень увлекательный подсчет</t>
+  </si>
+  <si>
+    <t>Скурпулезный оценка нарушений этапов</t>
+  </si>
+  <si>
+    <t>Скурпулезная оценка нарушений этапов</t>
+  </si>
+  <si>
+    <t>привела его на тот же землеописаной сечение</t>
+  </si>
+  <si>
+    <t>привела его на то же землеописаное сечение</t>
+  </si>
+  <si>
+    <t>хорошо предусмотрена эта естественная случай</t>
+  </si>
+  <si>
+    <t>хорошо предусмотрен этот естественный случай</t>
+  </si>
+  <si>
+    <t>случай требует скурпулезного оценки</t>
+  </si>
+  <si>
+    <t>случай требует скурпулезной оценки</t>
+  </si>
+  <si>
+    <t>не запретила основной множесте людей</t>
+  </si>
+  <si>
+    <t>не запретила основному множесту людей</t>
+  </si>
+  <si>
+    <t>с земной обществом произошла недопустимая случай</t>
+  </si>
+  <si>
+    <t>с земнойым обществом произошел недопустимый случай</t>
+  </si>
+  <si>
+    <t>оставляют ваш местоположение</t>
+  </si>
+  <si>
+    <t>оставляют ваше местоположение</t>
+  </si>
+  <si>
+    <t>энвольтировать</t>
+  </si>
+  <si>
+    <t>молекул нашего живой особи</t>
+  </si>
+  <si>
+    <t>молекул нашей живой особи</t>
+  </si>
+  <si>
+    <t>не содержался бы отрицательный обстоятельство</t>
+  </si>
+  <si>
+    <t>не содержалось бы отрицательное обстоятельство</t>
+  </si>
+  <si>
+    <t>В конце 1996 года в предновогодней беседе</t>
+  </si>
+  <si>
+    <t>В конце 1996 года в предновогоднем беседа</t>
+  </si>
+  <si>
+    <t>для чего была проведена Ооктябрьская мятеж</t>
+  </si>
+  <si>
+    <t>для чего была проведен Ооктябрьсийя мятеж</t>
+  </si>
+  <si>
+    <t>где зародился этот языческий поклонение</t>
+  </si>
+  <si>
+    <t>где зародилось   это языческое поклонение</t>
+  </si>
+  <si>
+    <t>Не потому ли всю поколение Рыб</t>
+  </si>
+  <si>
+    <t>Не потому ли все поколение Рыб</t>
+  </si>
+  <si>
+    <t>зачастую просто уродливую образу</t>
+  </si>
+  <si>
+    <t>зачастую просто уродливый образ</t>
+  </si>
+  <si>
+    <t>на всю земную общество</t>
+  </si>
+  <si>
+    <t>на все земное общество</t>
+  </si>
+  <si>
+    <t>Да и сама целительство по уши погрязла</t>
+  </si>
+  <si>
+    <t>Да и само целительство по уши погрязло</t>
+  </si>
+  <si>
+    <t>если вспомнить условный чертеж Несущих сведения Полей</t>
+  </si>
+  <si>
+    <t>если вспомнить условную чертеж несущих сведения Полей</t>
+  </si>
+  <si>
+    <t>еще один важный особенность</t>
+  </si>
+  <si>
+    <t>еще одна важная особенность</t>
+  </si>
+  <si>
+    <t>панспермии</t>
+  </si>
+  <si>
+    <t>не проводить изменение лунной витки</t>
+  </si>
+  <si>
+    <t>не проводить изменения лунных витков</t>
+  </si>
+  <si>
+    <t>забраться на главный высшая точка</t>
+  </si>
+  <si>
+    <t>забраться на главную высшую точку</t>
+  </si>
+  <si>
+    <t>своему семье безбедное существование</t>
+  </si>
+  <si>
+    <t>своей семье безбедное существование</t>
+  </si>
+  <si>
+    <t>в итоге всей этого случая</t>
+  </si>
+  <si>
+    <t>сериалу</t>
+  </si>
+  <si>
+    <t>дегустацию</t>
   </si>
 </sst>
 </file>
@@ -869,7 +1898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7256F3A-5CBA-4182-B90F-37645EE12738}">
-  <dimension ref="A2:B63"/>
+  <dimension ref="A2:B67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1195,6 +2224,26 @@
         <v>79</v>
       </c>
     </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>468</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1202,11 +2251,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:B34"/>
+  <dimension ref="A2:B204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.85546875" customWidth="1"/>
-    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="1" max="1" width="66.5703125" customWidth="1"/>
+    <col min="2" max="2" width="67.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1454,6 +2503,1363 @@
       </c>
       <c r="B34" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>142</v>
+      </c>
+      <c r="B43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>157</v>
+      </c>
+      <c r="B50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>194</v>
+      </c>
+      <c r="B69" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>196</v>
+      </c>
+      <c r="B70" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>200</v>
+      </c>
+      <c r="B72" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>202</v>
+      </c>
+      <c r="B73" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>204</v>
+      </c>
+      <c r="B74" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>206</v>
+      </c>
+      <c r="B75" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>208</v>
+      </c>
+      <c r="B76" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>210</v>
+      </c>
+      <c r="B77" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>212</v>
+      </c>
+      <c r="B78" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>214</v>
+      </c>
+      <c r="B79" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>216</v>
+      </c>
+      <c r="B80" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>218</v>
+      </c>
+      <c r="B81" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>220</v>
+      </c>
+      <c r="B82" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>222</v>
+      </c>
+      <c r="B83" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>224</v>
+      </c>
+      <c r="B84" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>228</v>
+      </c>
+      <c r="B86" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>230</v>
+      </c>
+      <c r="B87" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>233</v>
+      </c>
+      <c r="B88" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>234</v>
+      </c>
+      <c r="B89" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>236</v>
+      </c>
+      <c r="B90" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>238</v>
+      </c>
+      <c r="B91" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>240</v>
+      </c>
+      <c r="B92" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>242</v>
+      </c>
+      <c r="B93" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>244</v>
+      </c>
+      <c r="B94" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>246</v>
+      </c>
+      <c r="B95" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>248</v>
+      </c>
+      <c r="B96" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>250</v>
+      </c>
+      <c r="B97" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>252</v>
+      </c>
+      <c r="B98" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>254</v>
+      </c>
+      <c r="B99" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>256</v>
+      </c>
+      <c r="B100" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>258</v>
+      </c>
+      <c r="B101" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>260</v>
+      </c>
+      <c r="B102" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>262</v>
+      </c>
+      <c r="B103" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>264</v>
+      </c>
+      <c r="B104" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>266</v>
+      </c>
+      <c r="B105" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>269</v>
+      </c>
+      <c r="B106" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>270</v>
+      </c>
+      <c r="B107" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>272</v>
+      </c>
+      <c r="B108" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>274</v>
+      </c>
+      <c r="B109" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>276</v>
+      </c>
+      <c r="B110" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>278</v>
+      </c>
+      <c r="B111" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>280</v>
+      </c>
+      <c r="B112" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>282</v>
+      </c>
+      <c r="B113" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>284</v>
+      </c>
+      <c r="B114" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>286</v>
+      </c>
+      <c r="B115" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>288</v>
+      </c>
+      <c r="B116" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>291</v>
+      </c>
+      <c r="B117" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>292</v>
+      </c>
+      <c r="B118" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>294</v>
+      </c>
+      <c r="B119" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>296</v>
+      </c>
+      <c r="B120" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>298</v>
+      </c>
+      <c r="B121" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>300</v>
+      </c>
+      <c r="B122" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>302</v>
+      </c>
+      <c r="B123" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>304</v>
+      </c>
+      <c r="B124" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>306</v>
+      </c>
+      <c r="B125" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>308</v>
+      </c>
+      <c r="B126" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>310</v>
+      </c>
+      <c r="B127" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>313</v>
+      </c>
+      <c r="B128" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>314</v>
+      </c>
+      <c r="B129" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>316</v>
+      </c>
+      <c r="B130" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>318</v>
+      </c>
+      <c r="B131" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>320</v>
+      </c>
+      <c r="B132" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>322</v>
+      </c>
+      <c r="B133" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>324</v>
+      </c>
+      <c r="B134" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>326</v>
+      </c>
+      <c r="B135" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>328</v>
+      </c>
+      <c r="B136" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>330</v>
+      </c>
+      <c r="B137" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>332</v>
+      </c>
+      <c r="B138" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>334</v>
+      </c>
+      <c r="B139" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>336</v>
+      </c>
+      <c r="B140" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>338</v>
+      </c>
+      <c r="B141" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>340</v>
+      </c>
+      <c r="B142" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>342</v>
+      </c>
+      <c r="B143" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>344</v>
+      </c>
+      <c r="B144" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>346</v>
+      </c>
+      <c r="B145" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>348</v>
+      </c>
+      <c r="B146" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>350</v>
+      </c>
+      <c r="B147" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>352</v>
+      </c>
+      <c r="B148" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>354</v>
+      </c>
+      <c r="B149" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>356</v>
+      </c>
+      <c r="B150" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>358</v>
+      </c>
+      <c r="B151" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>360</v>
+      </c>
+      <c r="B152" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>362</v>
+      </c>
+      <c r="B153" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>364</v>
+      </c>
+      <c r="B154" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>366</v>
+      </c>
+      <c r="B155" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>368</v>
+      </c>
+      <c r="B156" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>370</v>
+      </c>
+      <c r="B157" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>372</v>
+      </c>
+      <c r="B158" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>374</v>
+      </c>
+      <c r="B159" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>376</v>
+      </c>
+      <c r="B160" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>378</v>
+      </c>
+      <c r="B161" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>380</v>
+      </c>
+      <c r="B162" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>382</v>
+      </c>
+      <c r="B163" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>384</v>
+      </c>
+      <c r="B164" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>386</v>
+      </c>
+      <c r="B165" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>388</v>
+      </c>
+      <c r="B166" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>390</v>
+      </c>
+      <c r="B167" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>392</v>
+      </c>
+      <c r="B168" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>394</v>
+      </c>
+      <c r="B169" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>396</v>
+      </c>
+      <c r="B170" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>398</v>
+      </c>
+      <c r="B171" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>400</v>
+      </c>
+      <c r="B172" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>402</v>
+      </c>
+      <c r="B173" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>404</v>
+      </c>
+      <c r="B174" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>406</v>
+      </c>
+      <c r="B175" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>408</v>
+      </c>
+      <c r="B176" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>410</v>
+      </c>
+      <c r="B177" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>412</v>
+      </c>
+      <c r="B178" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>414</v>
+      </c>
+      <c r="B179" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>416</v>
+      </c>
+      <c r="B180" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>418</v>
+      </c>
+      <c r="B181" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>420</v>
+      </c>
+      <c r="B182" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>422</v>
+      </c>
+      <c r="B183" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>424</v>
+      </c>
+      <c r="B184" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>426</v>
+      </c>
+      <c r="B185" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>428</v>
+      </c>
+      <c r="B186" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>430</v>
+      </c>
+      <c r="B187" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>432</v>
+      </c>
+      <c r="B188" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>434</v>
+      </c>
+      <c r="B189" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>437</v>
+      </c>
+      <c r="B190" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>439</v>
+      </c>
+      <c r="B191" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>442</v>
+      </c>
+      <c r="B192" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>443</v>
+      </c>
+      <c r="B193" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>445</v>
+      </c>
+      <c r="B194" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>447</v>
+      </c>
+      <c r="B195" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>449</v>
+      </c>
+      <c r="B196" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>451</v>
+      </c>
+      <c r="B197" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>453</v>
+      </c>
+      <c r="B198" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>456</v>
+      </c>
+      <c r="B199" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>457</v>
+      </c>
+      <c r="B200" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>460</v>
+      </c>
+      <c r="B201" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>462</v>
+      </c>
+      <c r="B202" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>464</v>
+      </c>
+      <c r="B203" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99365C30-77A5-4819-8F25-05B28DB7E96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4556D47-F23C-4F3D-AC24-E2C078C7A876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="975" windowWidth="18315" windowHeight="11565" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="675" yWindow="975" windowWidth="18315" windowHeight="11715" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="925">
   <si>
     <t>исходные</t>
   </si>
@@ -1975,12 +1975,873 @@
   <si>
     <t xml:space="preserve">мыслительная матрица начинала воплотить эти запахи </t>
   </si>
+  <si>
+    <t>был проведен полный оценка</t>
+  </si>
+  <si>
+    <t>быа проведена полнаая оценка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">уже был набран этот письменность, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">уже была  набрана эта письменность, </t>
+  </si>
+  <si>
+    <t>у власть имущих впал наш Сосредоточение</t>
+  </si>
+  <si>
+    <t>у власть имущих впало наше Сосредоточение</t>
+  </si>
+  <si>
+    <t>Подход современной исконного целительства</t>
+  </si>
+  <si>
+    <t>Подход современного исконного целительства</t>
+  </si>
+  <si>
+    <t>Современная целительство</t>
+  </si>
+  <si>
+    <t>Современное целительство</t>
+  </si>
+  <si>
+    <t>непонятных исконной целительстве заболеваний.</t>
+  </si>
+  <si>
+    <t>непонятных исконно целительских заболеваний.</t>
+  </si>
+  <si>
+    <t>появляется общий местоположение.</t>
+  </si>
+  <si>
+    <t>появляется общее местоположение.</t>
+  </si>
+  <si>
+    <t>Заболел жертва </t>
+  </si>
+  <si>
+    <t>Заболела жертва </t>
+  </si>
+  <si>
+    <t>Умер жертва</t>
+  </si>
+  <si>
+    <t>Умерла жертва</t>
+  </si>
+  <si>
+    <t>любая важнейшая случай </t>
+  </si>
+  <si>
+    <t>любой важнейший случай </t>
+  </si>
+  <si>
+    <t>Любая увечье, нанесенная человеку</t>
+  </si>
+  <si>
+    <t>Любые увечья, нанесенные человеку</t>
+  </si>
+  <si>
+    <t>любая увечье,</t>
+  </si>
+  <si>
+    <t>любые  увечья,</t>
+  </si>
+  <si>
+    <t>хирургические вмешательства,</t>
+  </si>
+  <si>
+    <t>хирургическое вмешательство,</t>
+  </si>
+  <si>
+    <t>международной целительской преступной устройством,</t>
+  </si>
+  <si>
+    <t>международным целительским преступным устройством,</t>
+  </si>
+  <si>
+    <t>торговавшей жертвенными органами</t>
+  </si>
+  <si>
+    <t>торговавшым жертвенными органами</t>
+  </si>
+  <si>
+    <t>так называемый абортный сырьё.</t>
+  </si>
+  <si>
+    <t>так называемое абортное сырьё.</t>
+  </si>
+  <si>
+    <t>в предыдущей перерождения</t>
+  </si>
+  <si>
+    <t>в предыдущем перерождении</t>
+  </si>
+  <si>
+    <t>своих жевательных чутья,</t>
+  </si>
+  <si>
+    <t>своих жевательных чувств</t>
+  </si>
+  <si>
+    <t>Этой вопросе посвящена постоянная</t>
+  </si>
+  <si>
+    <t>Этому вопросу посвящена постоянная</t>
+  </si>
+  <si>
+    <t>полная восстановление</t>
+  </si>
+  <si>
+    <t>полное восстановление</t>
+  </si>
+  <si>
+    <t>дистанционную изменение. </t>
+  </si>
+  <si>
+    <t>дистанционное изменение. </t>
+  </si>
+  <si>
+    <t>что любой связь с</t>
+  </si>
+  <si>
+    <t>что любая связь с</t>
+  </si>
+  <si>
+    <t>Общая изображение Установки Внедрения и</t>
+  </si>
+  <si>
+    <t>Общее изображение Установки Внедрения и</t>
+  </si>
+  <si>
+    <t>человека их природный сырьё содержится</t>
+  </si>
+  <si>
+    <t>человека ее природное сырьё содержится</t>
+  </si>
+  <si>
+    <t>населения этой небесного тела.</t>
+  </si>
+  <si>
+    <t>населения этого небесного тела.</t>
+  </si>
+  <si>
+    <t>людей непереносимая ответ</t>
+  </si>
+  <si>
+    <t>людей непереносимость ответ</t>
+  </si>
+  <si>
+    <t>Аллергический правило лежит и</t>
+  </si>
+  <si>
+    <t>Аллергическое правило лежит и</t>
+  </si>
+  <si>
+    <t>астматические ответа. </t>
+  </si>
+  <si>
+    <t>астматическийответ </t>
+  </si>
+  <si>
+    <t>Предыдущая перерождение</t>
+  </si>
+  <si>
+    <t>Предыдущее перерождение</t>
+  </si>
+  <si>
+    <t>помощь в полной изменения и налаживания</t>
+  </si>
+  <si>
+    <t>помощь в полном изменении и налаживании</t>
+  </si>
+  <si>
+    <t>из временные промежутки лжеразумности</t>
+  </si>
+  <si>
+    <t>из временных промежутков лжеразумности</t>
+  </si>
+  <si>
+    <t>разумной образе существования.</t>
+  </si>
+  <si>
+    <t>разумному образу существования.</t>
+  </si>
+  <si>
+    <t>любая образ враждебности</t>
+  </si>
+  <si>
+    <t>любой образ враждебности</t>
+  </si>
+  <si>
+    <t>подселений происходят полное</t>
+  </si>
+  <si>
+    <t>подселений происходит полное</t>
+  </si>
+  <si>
+    <t>любая изменение в возможной образе</t>
+  </si>
+  <si>
+    <t>любое изменение в возможном образе</t>
+  </si>
+  <si>
+    <t>Второй временным промежутком </t>
+  </si>
+  <si>
+    <t>Вторым временным промежутком </t>
+  </si>
+  <si>
+    <t>за колдовство в «легкой» образе,</t>
+  </si>
+  <si>
+    <t>за колдовство в «легком» образе,</t>
+  </si>
+  <si>
+    <t>недопустима магическая действие «загрызания»</t>
+  </si>
+  <si>
+    <t>недопустимо магическое действие «загрызания»</t>
+  </si>
+  <si>
+    <t>порезался о разбитую хранилищу.</t>
+  </si>
+  <si>
+    <t>порезался о разбитоехранилище.</t>
+  </si>
+  <si>
+    <t>полную изменение по налаживания</t>
+  </si>
+  <si>
+    <t>полное изменение по налаживанию</t>
+  </si>
+  <si>
+    <t>либо пережить сильный перенапряжение</t>
+  </si>
+  <si>
+    <t>либо пережить сильное перенапряжение</t>
+  </si>
+  <si>
+    <t>области наибольшей повреждения иммунной</t>
+  </si>
+  <si>
+    <t>области наибольшего повреждения иммунной</t>
+  </si>
+  <si>
+    <t>за счет жертвенного живой особи человека.</t>
+  </si>
+  <si>
+    <t>за счет жертвенной живой особи человека.</t>
+  </si>
+  <si>
+    <t>при проведении энергоинформационной изменения,</t>
+  </si>
+  <si>
+    <t>при проведении энергоинформационного изменения,</t>
+  </si>
+  <si>
+    <t>дать метастазную образу заболевания. </t>
+  </si>
+  <si>
+    <t>дать метастазный образ заболевания. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">на общую налаживание </t>
+  </si>
+  <si>
+    <t xml:space="preserve">на общее налаживание </t>
+  </si>
+  <si>
+    <t>выделится при полной крахе общества</t>
+  </si>
+  <si>
+    <t>выделится при полном крахе общества</t>
+  </si>
+  <si>
+    <t>«энергетический» возможность женщины становился меньше,</t>
+  </si>
+  <si>
+    <t>«энергетическая» возможность женщины становилась меньше,</t>
+  </si>
+  <si>
+    <t>проводился общий посещение</t>
+  </si>
+  <si>
+    <t>проводилось общее посещение</t>
+  </si>
+  <si>
+    <t>называли эту отдел ученых,</t>
+  </si>
+  <si>
+    <t>называли этот отдел ученых,</t>
+  </si>
+  <si>
+    <t>взять на оценка жидкость из легких</t>
+  </si>
+  <si>
+    <t>взять на оценку жидкость из легких</t>
+  </si>
+  <si>
+    <t>провели оценка внутрилегочной жидкости,</t>
+  </si>
+  <si>
+    <t>провели оценку внутрилегочной жидкости,</t>
+  </si>
+  <si>
+    <t>имени больные женщины, впервые принесшей</t>
+  </si>
+  <si>
+    <t>имени больной женщины, впервые принесшей</t>
+  </si>
+  <si>
+    <t>о состоянии собственной разума</t>
+  </si>
+  <si>
+    <t>о состоянии собственного разума</t>
+  </si>
+  <si>
+    <t>действительности отключается внедренной сущностью</t>
+  </si>
+  <si>
+    <t>действительности отключается внедренная сущностью</t>
+  </si>
+  <si>
+    <t>, какая сбой началась среди африканских «мужиков</t>
+  </si>
+  <si>
+    <t>, какая сбой начался среди африканских «мужиков</t>
+  </si>
+  <si>
+    <t>чрезвычайную множества своей Установки</t>
+  </si>
+  <si>
+    <t>чрезвычайное множество своей Установки</t>
+  </si>
+  <si>
+    <t>были заражены менингитоподобным заразой по всей</t>
+  </si>
+  <si>
+    <t>были заражены менингитоподобной заразой по всей</t>
+  </si>
+  <si>
+    <t>живой, разумная живая особь,</t>
+  </si>
+  <si>
+    <t>живой, разумный живая особь,</t>
+  </si>
+  <si>
+    <t>общество сам отобразил эти сведения</t>
+  </si>
+  <si>
+    <t>общество само отобразило эти сведения</t>
+  </si>
+  <si>
+    <t>запустил эту мыслеобраз в воплощение!</t>
+  </si>
+  <si>
+    <t>запустило этот мыслеобраз в воплощение!</t>
+  </si>
+  <si>
+    <t>имеющими обычный возможность и способности.</t>
+  </si>
+  <si>
+    <t>имеющими обычную возможность и способности.</t>
+  </si>
+  <si>
+    <t>бред из области “гражданской” вымысле.</t>
+  </si>
+  <si>
+    <t>бред из области “гражданского” вымысла.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в вооружённые силы пытались </t>
+  </si>
+  <si>
+    <t xml:space="preserve">в вооружённых силах пытались </t>
+  </si>
+  <si>
+    <t>время в вооружённые силы любят</t>
+  </si>
+  <si>
+    <t>время в вооружённых силах любят</t>
+  </si>
+  <si>
+    <t>перезапись всей сведениям</t>
+  </si>
+  <si>
+    <t>перезапись всех сведений</t>
+  </si>
+  <si>
+    <t>итоге такой насильственной перезаписи</t>
+  </si>
+  <si>
+    <t>итоге такая насильственная перезапись</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вооружённые силы для защиты земли </t>
+  </si>
+  <si>
+    <t xml:space="preserve">вооружённых сил для защиты земли </t>
+  </si>
+  <si>
+    <t>неотъемлемым свойством вооружённые силы.</t>
+  </si>
+  <si>
+    <t>неотъемлемым свойством вооружённых сил.</t>
+  </si>
+  <si>
+    <t>У био-роботов, согласно основному разработке Системы,</t>
+  </si>
+  <si>
+    <t>У био-роботов, согласно основной разработке Системы,</t>
+  </si>
+  <si>
+    <t>Какая может быть согласование,</t>
+  </si>
+  <si>
+    <t>Какое может быть согласование,</t>
+  </si>
+  <si>
+    <t>нарушение обычной уровня тепла желез,</t>
+  </si>
+  <si>
+    <t>нарушение обычного  уровня тепла желез,</t>
+  </si>
+  <si>
+    <t>во временной промежуток их полового созревания</t>
+  </si>
+  <si>
+    <t>во временном промежутке их полового созревания</t>
+  </si>
+  <si>
+    <t>в вооружённые силы.</t>
+  </si>
+  <si>
+    <t>в вооружённых силах.</t>
+  </si>
+  <si>
+    <t>постоянный перенапряжение.</t>
+  </si>
+  <si>
+    <t>постоянное перенапряжение.</t>
+  </si>
+  <si>
+    <t>через исконную целительство.</t>
+  </si>
+  <si>
+    <t>через исконное целительство.</t>
+  </si>
+  <si>
+    <t>может повлечь за собой цепную ответ</t>
+  </si>
+  <si>
+    <t>может повлечь за собой цепной ответ</t>
+  </si>
+  <si>
+    <t>Подобную изменение необходимо</t>
+  </si>
+  <si>
+    <t>Подобное изменение необходимо</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При изменения детородных возможностей </t>
+  </si>
+  <si>
+    <t xml:space="preserve">При изменении детородных возможностей </t>
+  </si>
+  <si>
+    <t>установку Космического Жертвенности</t>
+  </si>
+  <si>
+    <t>установку Космической Жертвенности</t>
+  </si>
+  <si>
+    <t>сразу на изменения вспоминают о</t>
+  </si>
+  <si>
+    <t>сразу на изменении вспоминают о</t>
+  </si>
+  <si>
+    <t>помощь «братьям» в налаживания их</t>
+  </si>
+  <si>
+    <t>помощь «братьям» в налаживании их</t>
+  </si>
+  <si>
+    <t>когда её необходимо</t>
+  </si>
+  <si>
+    <t>когда ей необходимо</t>
+  </si>
+  <si>
+    <t>в этой нелегкой случая</t>
+  </si>
+  <si>
+    <t>в этом нелегком случае</t>
+  </si>
+  <si>
+    <t>ухудшении природных условиях беременность</t>
+  </si>
+  <si>
+    <t>ухудшении природных условий беременность</t>
+  </si>
+  <si>
+    <t>в женской собеседования.</t>
+  </si>
+  <si>
+    <t>в женском собеседовании</t>
+  </si>
+  <si>
+    <t>Это особа установка</t>
+  </si>
+  <si>
+    <t>Это особая  установка</t>
+  </si>
+  <si>
+    <t>скрывается весь тайна</t>
+  </si>
+  <si>
+    <t>скрывается вся тайна</t>
+  </si>
+  <si>
+    <t>устройстве крови вызывает мышечную запрет.</t>
+  </si>
+  <si>
+    <t>устройстве крови вызывает мышечный запрет.</t>
+  </si>
+  <si>
+    <t>повышенного электро-притяжательного обстановки являются</t>
+  </si>
+  <si>
+    <t>повышенной электро-притяжательной обстановки являются</t>
+  </si>
+  <si>
+    <t>превышает естественный обстановка Земли</t>
+  </si>
+  <si>
+    <t>превышает естественную обстановка Земли</t>
+  </si>
+  <si>
+    <t>противоречит общепринятой мировоззрения</t>
+  </si>
+  <si>
+    <t>противоречит общепринятому мировоззрению</t>
+  </si>
+  <si>
+    <t>этой самой мировоззрения не противоречит</t>
+  </si>
+  <si>
+    <t>этому самому мировоззрению не противоречит</t>
+  </si>
+  <si>
+    <t>же после вооружённые силы</t>
+  </si>
+  <si>
+    <t>же после вооружённых сил</t>
+  </si>
+  <si>
+    <t>с записями беседа прошедших</t>
+  </si>
+  <si>
+    <t>с записями бесед прошедших</t>
+  </si>
+  <si>
+    <t>Увлекательная сведения при этом была выявлена.</t>
+  </si>
+  <si>
+    <t>Увлекательнае сведения при этом были выявлены.</t>
+  </si>
+  <si>
+    <t>своя, заранее определенная значение…</t>
+  </si>
+  <si>
+    <t>свое, заранее определенное значение…</t>
+  </si>
+  <si>
+    <t>Многие целители в своей применении</t>
+  </si>
+  <si>
+    <t>Многие целители в своем применении</t>
+  </si>
+  <si>
+    <t>наступила налаживания</t>
+  </si>
+  <si>
+    <t>наступило налаживание</t>
+  </si>
+  <si>
+    <t>свидетельство там важный был. </t>
+  </si>
+  <si>
+    <t>свидетельство там важное было. </t>
+  </si>
+  <si>
+    <t>провести полную налаживание</t>
+  </si>
+  <si>
+    <t>провести полное налаживание</t>
+  </si>
+  <si>
+    <t>Общая чертёж проведения личной изменения с</t>
+  </si>
+  <si>
+    <t>Общий чертёж проведения личного изменения с</t>
+  </si>
+  <si>
+    <t> покаяния изменение будет просто бессмысленна.</t>
+  </si>
+  <si>
+    <t> покаяния изменение будет просто бессмысленно</t>
+  </si>
+  <si>
+    <t>как бы начинает всю изменение сначала.</t>
+  </si>
+  <si>
+    <t>как бы начинает все изменение сначала.</t>
+  </si>
+  <si>
+    <t>больной был в связующей случая с ВР и Установка</t>
+  </si>
+  <si>
+    <t>больной был в связующем случае с ВР и Установка</t>
+  </si>
+  <si>
+    <t>зображение при налаживания воплощения меняется</t>
+  </si>
+  <si>
+    <t>зображение при налаживании воплощения меняется</t>
+  </si>
+  <si>
+    <t>тем более, фиолетовый обстановка</t>
+  </si>
+  <si>
+    <t>тем более, фиолетовую обстановку</t>
+  </si>
+  <si>
+    <t>определённый местоположение в Несущих сведения</t>
+  </si>
+  <si>
+    <t>определённое местоположение в Несущих сведения</t>
+  </si>
+  <si>
+    <t>чем при личной изменения.</t>
+  </si>
+  <si>
+    <t>чем при личном изменении.</t>
+  </si>
+  <si>
+    <t> собой обобщенный приведение всех людей</t>
+  </si>
+  <si>
+    <t> собой обобщенное приведение всех людей</t>
+  </si>
+  <si>
+    <t>При проведении удалённой изменения </t>
+  </si>
+  <si>
+    <t>При проведении удалённого изменения </t>
+  </si>
+  <si>
+    <t>проведении удалённой изменения в любой ее образе</t>
+  </si>
+  <si>
+    <t>проведении удалённого изменения в любом ее образе</t>
+  </si>
+  <si>
+    <t>возникнуть неисправная случай</t>
+  </si>
+  <si>
+    <t>возникнуть неисправный случай</t>
+  </si>
+  <si>
+    <t>Вместо изменения по налаживания</t>
+  </si>
+  <si>
+    <t>Вместо изменения по налаживанию</t>
+  </si>
+  <si>
+    <t>при удалённой и при личной изменения</t>
+  </si>
+  <si>
+    <t>при удалённом и при личном  изменении</t>
+  </si>
+  <si>
+    <t>была создана следующая мыслеобраз:</t>
+  </si>
+  <si>
+    <t>был создан  следующий мыслеобраз:</t>
+  </si>
+  <si>
+    <t>весь посещение «держать» его перед</t>
+  </si>
+  <si>
+    <t>все посещение «держать» его перед</t>
+  </si>
+  <si>
+    <t>даже целому колдовскому семье. </t>
+  </si>
+  <si>
+    <t>даже целой колдовской семье. </t>
+  </si>
+  <si>
+    <t>пожелавшего в новой воплощения сменить клавиатуру</t>
+  </si>
+  <si>
+    <t>пожелавшего в новом воплощении сменить клавиатуру</t>
+  </si>
+  <si>
+    <t>чтобы ваша мыслеобраз вышла в воплощение</t>
+  </si>
+  <si>
+    <t>чтобы ваш мыслеобраз вошел в воплощение</t>
+  </si>
+  <si>
+    <t>потом отпустить эту мыслеобраз</t>
+  </si>
+  <si>
+    <t>потом отпустить этот мыслеобраз</t>
+  </si>
+  <si>
+    <t>вызвало бурный недовольство «смотрителей»</t>
+  </si>
+  <si>
+    <t>вызвало бурное недовольство «смотрителей»</t>
+  </si>
+  <si>
+    <t>Однако их чрезвычайная множество уже</t>
+  </si>
+  <si>
+    <t>Однако их чрезвычайное множество уже</t>
+  </si>
+  <si>
+    <t>до прямой воплощения.</t>
+  </si>
+  <si>
+    <t>до прямого воплощения.</t>
+  </si>
+  <si>
+    <t>это обычный власть научных разработок</t>
+  </si>
+  <si>
+    <t>это обычная власть научных разработок</t>
+  </si>
+  <si>
+    <t> был объявлен очередной горе, </t>
+  </si>
+  <si>
+    <t> был объявлено очередное горе, </t>
+  </si>
+  <si>
+    <t>При составление вездесущего предсказания</t>
+  </si>
+  <si>
+    <t>При составлении вездесущего предсказания</t>
+  </si>
+  <si>
+    <t>Обнародование в ростовских бумажным изданиях</t>
+  </si>
+  <si>
+    <t>Обнародование в ростовских бумажных изданиях</t>
+  </si>
+  <si>
+    <t>Подобная случай – нереализованность увиденного </t>
+  </si>
+  <si>
+    <t>Подобный случай – нереализованность увиденного </t>
+  </si>
+  <si>
+    <t>производится промежуточная изменение,</t>
+  </si>
+  <si>
+    <t>производится промежуточное изменение,</t>
+  </si>
+  <si>
+    <t>это просто «круглая» день, позволяющая оправдать</t>
+  </si>
+  <si>
+    <t>это просто «круглый» день, позволяющий оправдать</t>
+  </si>
+  <si>
+    <t>кто весь этот представление «подогревал</t>
+  </si>
+  <si>
+    <t>кто все это  представление «подогревал</t>
+  </si>
+  <si>
+    <t>Мыслеобраза при проведении общей изменения</t>
+  </si>
+  <si>
+    <t>Мыслеобраза при проведении общего изменения</t>
+  </si>
+  <si>
+    <t>кто задавал данную отрицательную случай </t>
+  </si>
+  <si>
+    <t>кто задавал данный отрицательный случай </t>
+  </si>
+  <si>
+    <t>вернуть весь изъятый возможность!</t>
+  </si>
+  <si>
+    <t>вернуть всю изъятую возможность!</t>
+  </si>
+  <si>
+    <t>образование властной порядка</t>
+  </si>
+  <si>
+    <t>образование властного порядка</t>
+  </si>
+  <si>
+    <t> клевретов,</t>
+  </si>
+  <si>
+    <t>воздействия этих же способности у клевретов</t>
+  </si>
+  <si>
+    <t>воздействием этих же способностей у клевретов</t>
+  </si>
+  <si>
+    <t>Это достоверная случай борьбы</t>
+  </si>
+  <si>
+    <t>Это достоверный случай борьбы</t>
+  </si>
+  <si>
+    <t>с ужасом ждали этой дни,</t>
+  </si>
+  <si>
+    <t>с ужасом ждали этого дня,</t>
+  </si>
+  <si>
+    <t>выплеснула в космос всю накопленную заряд</t>
+  </si>
+  <si>
+    <t>выплеснуло в космос весь накопленный заряд</t>
+  </si>
+  <si>
+    <t>пошел на убыль и в какой-то особенность стал равен</t>
+  </si>
+  <si>
+    <t>пошел на убыль и в какою-то особенность стало равно</t>
+  </si>
+  <si>
+    <t>В обычной чёрного колдовства это называется</t>
+  </si>
+  <si>
+    <t>В обычном чёрном колдовстве это называется</t>
+  </si>
+  <si>
+    <t>Это очень тонкий особенность. </t>
+  </si>
+  <si>
+    <t>Это очень тонкая особенность. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2052,6 +2913,23 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="LiberEmb"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="LiberEmb"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="LiberEmb"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2085,7 +2963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2099,6 +2977,12 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2433,7 +3317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7256F3A-5CBA-4182-B90F-37645EE12738}">
-  <dimension ref="A2:B69"/>
+  <dimension ref="A2:B70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -2789,6 +3673,11 @@
         <v>595</v>
       </c>
     </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="12" t="s">
+        <v>910</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2796,7 +3685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:B287"/>
+  <dimension ref="A2:B431"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="72" style="7" customWidth="1"/>
@@ -5072,6 +5961,1158 @@
       </c>
       <c r="B287" t="s">
         <v>636</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" t="s">
+        <v>638</v>
+      </c>
+      <c r="B288" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" t="s">
+        <v>640</v>
+      </c>
+      <c r="B289" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="B292" s="11" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" t="s">
+        <v>660</v>
+      </c>
+      <c r="B299" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" t="s">
+        <v>662</v>
+      </c>
+      <c r="B300" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" t="s">
+        <v>664</v>
+      </c>
+      <c r="B301" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" t="s">
+        <v>666</v>
+      </c>
+      <c r="B302" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" t="s">
+        <v>670</v>
+      </c>
+      <c r="B304" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" t="s">
+        <v>674</v>
+      </c>
+      <c r="B306" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B307" s="12" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="B308" s="12" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" t="s">
+        <v>680</v>
+      </c>
+      <c r="B309" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" t="s">
+        <v>682</v>
+      </c>
+      <c r="B310" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" t="s">
+        <v>684</v>
+      </c>
+      <c r="B311" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" t="s">
+        <v>686</v>
+      </c>
+      <c r="B312" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="B313" s="12" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="B317" s="12" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" t="s">
+        <v>698</v>
+      </c>
+      <c r="B318" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="B321" s="12" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" t="s">
+        <v>706</v>
+      </c>
+      <c r="B322" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" t="s">
+        <v>712</v>
+      </c>
+      <c r="B325" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" t="s">
+        <v>720</v>
+      </c>
+      <c r="B329" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" t="s">
+        <v>728</v>
+      </c>
+      <c r="B333" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" t="s">
+        <v>730</v>
+      </c>
+      <c r="B334" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" t="s">
+        <v>732</v>
+      </c>
+      <c r="B335" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" t="s">
+        <v>736</v>
+      </c>
+      <c r="B337" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" t="s">
+        <v>738</v>
+      </c>
+      <c r="B338" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" t="s">
+        <v>746</v>
+      </c>
+      <c r="B342" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" t="s">
+        <v>748</v>
+      </c>
+      <c r="B343" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" t="s">
+        <v>752</v>
+      </c>
+      <c r="B345" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" t="s">
+        <v>754</v>
+      </c>
+      <c r="B346" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" t="s">
+        <v>756</v>
+      </c>
+      <c r="B347" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B349" s="7" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" t="s">
+        <v>766</v>
+      </c>
+      <c r="B352" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" t="s">
+        <v>776</v>
+      </c>
+      <c r="B357" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" t="s">
+        <v>780</v>
+      </c>
+      <c r="B359" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" t="s">
+        <v>782</v>
+      </c>
+      <c r="B360" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" t="s">
+        <v>788</v>
+      </c>
+      <c r="B363" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" t="s">
+        <v>790</v>
+      </c>
+      <c r="B364" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" t="s">
+        <v>796</v>
+      </c>
+      <c r="B367" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" t="s">
+        <v>798</v>
+      </c>
+      <c r="B368" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" t="s">
+        <v>800</v>
+      </c>
+      <c r="B369" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" t="s">
+        <v>806</v>
+      </c>
+      <c r="B372" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" t="s">
+        <v>808</v>
+      </c>
+      <c r="B373" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" t="s">
+        <v>816</v>
+      </c>
+      <c r="B377" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" t="s">
+        <v>818</v>
+      </c>
+      <c r="B378" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" t="s">
+        <v>822</v>
+      </c>
+      <c r="B380" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" t="s">
+        <v>824</v>
+      </c>
+      <c r="B381" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" t="s">
+        <v>828</v>
+      </c>
+      <c r="B383" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" t="s">
+        <v>830</v>
+      </c>
+      <c r="B384" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" t="s">
+        <v>832</v>
+      </c>
+      <c r="B385" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" t="s">
+        <v>838</v>
+      </c>
+      <c r="B388" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" t="s">
+        <v>840</v>
+      </c>
+      <c r="B389" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" t="s">
+        <v>333</v>
+      </c>
+      <c r="B390" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" t="s">
+        <v>846</v>
+      </c>
+      <c r="B393" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" t="s">
+        <v>852</v>
+      </c>
+      <c r="B396" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" t="s">
+        <v>860</v>
+      </c>
+      <c r="B400" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" t="s">
+        <v>864</v>
+      </c>
+      <c r="B402" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" t="s">
+        <v>866</v>
+      </c>
+      <c r="B403" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" t="s">
+        <v>870</v>
+      </c>
+      <c r="B405" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="B406" s="12" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" t="s">
+        <v>874</v>
+      </c>
+      <c r="B407" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" t="s">
+        <v>876</v>
+      </c>
+      <c r="B408" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" t="s">
+        <v>880</v>
+      </c>
+      <c r="B410" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" t="s">
+        <v>882</v>
+      </c>
+      <c r="B411" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" t="s">
+        <v>884</v>
+      </c>
+      <c r="B412" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" t="s">
+        <v>886</v>
+      </c>
+      <c r="B413" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" t="s">
+        <v>890</v>
+      </c>
+      <c r="B415" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="B416" s="5" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="B417" s="13" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" t="s">
+        <v>896</v>
+      </c>
+      <c r="B418" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" t="s">
+        <v>898</v>
+      </c>
+      <c r="B419" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" t="s">
+        <v>900</v>
+      </c>
+      <c r="B420" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" t="s">
+        <v>902</v>
+      </c>
+      <c r="B421" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="14" t="s">
+        <v>904</v>
+      </c>
+      <c r="B422" s="14" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="12" t="s">
+        <v>906</v>
+      </c>
+      <c r="B423" s="12" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" t="s">
+        <v>911</v>
+      </c>
+      <c r="B425" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" t="s">
+        <v>915</v>
+      </c>
+      <c r="B427" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" t="s">
+        <v>919</v>
+      </c>
+      <c r="B429" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" t="s">
+        <v>921</v>
+      </c>
+      <c r="B430" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="B431" s="5" t="s">
+        <v>924</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4556D47-F23C-4F3D-AC24-E2C078C7A876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224BF818-4A0A-4A97-96A2-37BD358B4E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="675" yWindow="975" windowWidth="18315" windowHeight="11715" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>

--- a/исправления внести/слова.xlsx
+++ b/исправления внести/слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224BF818-4A0A-4A97-96A2-37BD358B4E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D318ED5D-51B1-48DF-A000-21C4E9F760B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="975" windowWidth="18315" windowHeight="11715" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="одичночные" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1299">
   <si>
     <t>исходные</t>
   </si>
@@ -2835,6 +2835,1128 @@
   </si>
   <si>
     <t>Это очень тонкая особенность. </t>
+  </si>
+  <si>
+    <t>пентакля</t>
+  </si>
+  <si>
+    <t>магический талисман</t>
+  </si>
+  <si>
+    <t>приспешник</t>
+  </si>
+  <si>
+    <t>жанр фильма или телесериала</t>
+  </si>
+  <si>
+    <t>список товаров и услуг с указанием цен</t>
+  </si>
+  <si>
+    <t>оценивание вкусов запахов и других характеристик товара</t>
+  </si>
+  <si>
+    <t>смесь всяких семян</t>
+  </si>
+  <si>
+    <t>изготовление куклы  образа человека с использованием его фотографий</t>
+  </si>
+  <si>
+    <t>тонкая пленка обладающая избирательной проницаемостью</t>
+  </si>
+  <si>
+    <t>дорожно транспортное пришествие</t>
+  </si>
+  <si>
+    <t>ваш индивидуаьный гороскоп рождения</t>
+  </si>
+  <si>
+    <t>отрицание повторного перерождения души</t>
+  </si>
+  <si>
+    <t>звуковые волны неслышимые для человека</t>
+  </si>
+  <si>
+    <t>стрруктурный элемент клеточного ядра содержащая опрелененный набор генов</t>
+  </si>
+  <si>
+    <t>тип лучистой энергии невидимый для глаза</t>
+  </si>
+  <si>
+    <t>невидимое человеческому глазу электроиагнитное излучение</t>
+  </si>
+  <si>
+    <t>неисправленные</t>
+  </si>
+  <si>
+    <t>вещества природного и синтетического происхождения для лечения живыхорганизмов</t>
+  </si>
+  <si>
+    <t>устройство изменяющее параметры несущего сигнала</t>
+  </si>
+  <si>
+    <t>невидимая оболочка вокруг живых существ</t>
+  </si>
+  <si>
+    <t>способность живых  организмов ориентироваться в прстранстве</t>
+  </si>
+  <si>
+    <t>место еонтактк между двумя нейронами</t>
+  </si>
+  <si>
+    <t>частица являющаяся основным составляющим атомного ядра</t>
+  </si>
+  <si>
+    <t>отвлеченный</t>
+  </si>
+  <si>
+    <t>раздел медицины изучающий опухоли</t>
+  </si>
+  <si>
+    <t>цирк</t>
+  </si>
+  <si>
+    <t>потешище</t>
+  </si>
+  <si>
+    <t>клевретов</t>
+  </si>
+  <si>
+    <t>товарищ</t>
+  </si>
+  <si>
+    <t>условный отвлеченный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">агентство </t>
+  </si>
+  <si>
+    <t>компания организация</t>
+  </si>
+  <si>
+    <t>адвокатов</t>
+  </si>
+  <si>
+    <t>защитник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">адресоносителем </t>
+  </si>
+  <si>
+    <t>хранитель адреса</t>
+  </si>
+  <si>
+    <t>аквариуме</t>
+  </si>
+  <si>
+    <t>прозрачный сосуд для рыб</t>
+  </si>
+  <si>
+    <t>любитель аквариумов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">алкогольных </t>
+  </si>
+  <si>
+    <t>хмельной спиртной</t>
+  </si>
+  <si>
+    <t>аминокислот</t>
+  </si>
+  <si>
+    <t>лорганические соединения белков</t>
+  </si>
+  <si>
+    <t>ангины</t>
+  </si>
+  <si>
+    <t>инфекционное заболевание миндалин</t>
+  </si>
+  <si>
+    <t>антивещество</t>
+  </si>
+  <si>
+    <t>антипод</t>
+  </si>
+  <si>
+    <t>противоположный</t>
+  </si>
+  <si>
+    <t>отрицающий переселение душ</t>
+  </si>
+  <si>
+    <t>первобытность дикость темнота</t>
+  </si>
+  <si>
+    <t xml:space="preserve">антропологов </t>
+  </si>
+  <si>
+    <t>спец по эволюции людей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">аркана </t>
+  </si>
+  <si>
+    <t>канат петля шнур трос</t>
+  </si>
+  <si>
+    <t xml:space="preserve">астрофизические </t>
+  </si>
+  <si>
+    <t>звездный космический небесный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">атеросклеротические </t>
+  </si>
+  <si>
+    <t>хроническое заболевание артерий</t>
+  </si>
+  <si>
+    <t>атлас</t>
+  </si>
+  <si>
+    <t>книга альбом карта</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> свечение атмосфера биополе</t>
+  </si>
+  <si>
+    <t>бактерий</t>
+  </si>
+  <si>
+    <t>микроб микроорганизм</t>
+  </si>
+  <si>
+    <t>биолазера</t>
+  </si>
+  <si>
+    <t>аппарат биолазерный</t>
+  </si>
+  <si>
+    <t>способность живых сущуств ощущать скрытые объекты</t>
+  </si>
+  <si>
+    <t>жизненное поле</t>
+  </si>
+  <si>
+    <t>целитель</t>
+  </si>
+  <si>
+    <t>целительные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">борону </t>
+  </si>
+  <si>
+    <t>грабли плоскорез</t>
+  </si>
+  <si>
+    <t>браконьером</t>
+  </si>
+  <si>
+    <t>нарушитель охотничьих правил</t>
+  </si>
+  <si>
+    <t>бронхиты</t>
+  </si>
+  <si>
+    <t>воспаление бронхов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">варикозному </t>
+  </si>
+  <si>
+    <t>расширение вен нижних конечностей</t>
+  </si>
+  <si>
+    <t>внутрипарный</t>
+  </si>
+  <si>
+    <t>внутригрупповой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">высокоэнергетичных </t>
+  </si>
+  <si>
+    <t>высокозатратных</t>
+  </si>
+  <si>
+    <t>гарнитурой</t>
+  </si>
+  <si>
+    <t>комплект наушников комплект набор</t>
+  </si>
+  <si>
+    <t>гастарбайтерами</t>
+  </si>
+  <si>
+    <t>рабочий мигрант</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гастритом </t>
+  </si>
+  <si>
+    <t>воспаление желудка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гелиоцентрической </t>
+  </si>
+  <si>
+    <t>представление что Солнце является центральным небесным телом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гемаралитических </t>
+  </si>
+  <si>
+    <t>разрушуние эритрицитов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">генеалогических </t>
+  </si>
+  <si>
+    <t>фамильных родовых потомственых</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гены </t>
+  </si>
+  <si>
+    <t>наследственный материал  ДНК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">геоцентрической </t>
+  </si>
+  <si>
+    <t>центрированный на Земле</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гербицидов </t>
+  </si>
+  <si>
+    <t>ядохимикаты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гильотина </t>
+  </si>
+  <si>
+    <t>ножницы эшафот резак</t>
+  </si>
+  <si>
+    <t>гипертония</t>
+  </si>
+  <si>
+    <t>высокое кровяное давление</t>
+  </si>
+  <si>
+    <t>глюонного</t>
+  </si>
+  <si>
+    <t>безмассовая частица</t>
+  </si>
+  <si>
+    <t>голографии</t>
+  </si>
+  <si>
+    <t>обьемная фотография</t>
+  </si>
+  <si>
+    <t>государством</t>
+  </si>
+  <si>
+    <t>страна федерация власть республика правительство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гримасой </t>
+  </si>
+  <si>
+    <t>выражение лица кривляние</t>
+  </si>
+  <si>
+    <t xml:space="preserve">губернатор </t>
+  </si>
+  <si>
+    <t>глава администрации глава региона вождь начальник</t>
+  </si>
+  <si>
+    <t>дебилизм</t>
+  </si>
+  <si>
+    <t>кретинизм слабоумие тупизна</t>
+  </si>
+  <si>
+    <t>проба</t>
+  </si>
+  <si>
+    <t xml:space="preserve">декламированием </t>
+  </si>
+  <si>
+    <t>чтение произнесение</t>
+  </si>
+  <si>
+    <t>дескать</t>
+  </si>
+  <si>
+    <t>мол якобы значит</t>
+  </si>
+  <si>
+    <t>деспотизмов</t>
+  </si>
+  <si>
+    <t>властность  насилие тирания деспотичность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">децетратной </t>
+  </si>
+  <si>
+    <t>кровь от  трупа</t>
+  </si>
+  <si>
+    <t>диване</t>
+  </si>
+  <si>
+    <t>кровать постель кушетка софа</t>
+  </si>
+  <si>
+    <t>домогательства</t>
+  </si>
+  <si>
+    <t>насилие притязания оскорбление прниставание</t>
+  </si>
+  <si>
+    <t>жернова</t>
+  </si>
+  <si>
+    <t>круг мельница</t>
+  </si>
+  <si>
+    <t>махающий руками</t>
+  </si>
+  <si>
+    <t>низкий грубый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">запараллелено </t>
+  </si>
+  <si>
+    <t>уравнено согласовано составлено</t>
+  </si>
+  <si>
+    <t>зоопарк</t>
+  </si>
+  <si>
+    <t>зоосад зверинец</t>
+  </si>
+  <si>
+    <t>икон</t>
+  </si>
+  <si>
+    <t>лицо образ изображение</t>
+  </si>
+  <si>
+    <t>защитную</t>
+  </si>
+  <si>
+    <t>калека  убогий</t>
+  </si>
+  <si>
+    <t>инквизиция</t>
+  </si>
+  <si>
+    <t>пытка мучение терзание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">интернационалист </t>
+  </si>
+  <si>
+    <t>мирожитель гражданин мира</t>
+  </si>
+  <si>
+    <t>тепловой термический</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ионизированных </t>
+  </si>
+  <si>
+    <t>осеребреный</t>
+  </si>
+  <si>
+    <t>кадилом</t>
+  </si>
+  <si>
+    <t>сосуд богородское  зелье</t>
+  </si>
+  <si>
+    <t>период война  деятельность работа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кандидатский </t>
+  </si>
+  <si>
+    <t>ученый докторский научный</t>
+  </si>
+  <si>
+    <t>канюли</t>
+  </si>
+  <si>
+    <t>зонд катетер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">квиконса </t>
+  </si>
+  <si>
+    <t>минорный постоянно  скрытый аспект</t>
+  </si>
+  <si>
+    <t>приспособленец шестерка</t>
+  </si>
+  <si>
+    <t>зашифрованная закодированная</t>
+  </si>
+  <si>
+    <t>вахта поездка поручение</t>
+  </si>
+  <si>
+    <t>кондиции</t>
+  </si>
+  <si>
+    <t>тонус условия состояние</t>
+  </si>
+  <si>
+    <t>звездный небесный мировой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кристаллизации </t>
+  </si>
+  <si>
+    <t>затвердевание  отвердевание</t>
+  </si>
+  <si>
+    <t>лучевых</t>
+  </si>
+  <si>
+    <t>ламинат</t>
+  </si>
+  <si>
+    <t>искуственный паркет</t>
+  </si>
+  <si>
+    <t>ларингиты</t>
+  </si>
+  <si>
+    <t>воспаление гортани</t>
+  </si>
+  <si>
+    <t>лейкоцитов</t>
+  </si>
+  <si>
+    <t>кровяные тельца</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ленте </t>
+  </si>
+  <si>
+    <t>полоса бумага скотч</t>
+  </si>
+  <si>
+    <t>лигатурами</t>
+  </si>
+  <si>
+    <t>сязки букв</t>
+  </si>
+  <si>
+    <t>мамаи</t>
+  </si>
+  <si>
+    <t>богатырь воевода воин</t>
+  </si>
+  <si>
+    <t>лекарство снадобье</t>
+  </si>
+  <si>
+    <t>перепонка покров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">менталитете </t>
+  </si>
+  <si>
+    <t>ум мышление мировозрение</t>
+  </si>
+  <si>
+    <t>система знаков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">метеоритной </t>
+  </si>
+  <si>
+    <t>падающей звездной космичечкой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мишенями </t>
+  </si>
+  <si>
+    <t>цель объект щит</t>
+  </si>
+  <si>
+    <t>регулятор преобразователь</t>
+  </si>
+  <si>
+    <t>молекула</t>
+  </si>
+  <si>
+    <t>комплекс частица соединение</t>
+  </si>
+  <si>
+    <t>формирующий структурный</t>
+  </si>
+  <si>
+    <t>мыльных опер»</t>
+  </si>
+  <si>
+    <t>мелодрамы</t>
+  </si>
+  <si>
+    <t>негэнтропию,</t>
+  </si>
+  <si>
+    <t>порядок системность гармония</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нейролингвистического </t>
+  </si>
+  <si>
+    <t>нейроязыковый</t>
+  </si>
+  <si>
+    <t>неисправленых необработанных</t>
+  </si>
+  <si>
+    <t>обезличивание обобщение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">низкоэнергетические </t>
+  </si>
+  <si>
+    <t>экономичные энергосберегающие</t>
+  </si>
+  <si>
+    <t>излтопы радионуклиды</t>
+  </si>
+  <si>
+    <t>ядерная частица</t>
+  </si>
+  <si>
+    <t xml:space="preserve">одномандатные </t>
+  </si>
+  <si>
+    <t>одноместные персональные уникальные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">окроплял </t>
+  </si>
+  <si>
+    <t>брызгал проливал</t>
+  </si>
+  <si>
+    <t>олимп</t>
+  </si>
+  <si>
+    <t>высота вершина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">онанизму </t>
+  </si>
+  <si>
+    <t>ручная рабрта самостимуляция</t>
+  </si>
+  <si>
+    <t>опер</t>
+  </si>
+  <si>
+    <t>язык театр искусство</t>
+  </si>
+  <si>
+    <t>оптики</t>
+  </si>
+  <si>
+    <t>линзы бинокли  лупы</t>
+  </si>
+  <si>
+    <t>часть тело система</t>
+  </si>
+  <si>
+    <t>оргиями</t>
+  </si>
+  <si>
+    <t>развраи гулянка</t>
+  </si>
+  <si>
+    <t>орденоносец</t>
+  </si>
+  <si>
+    <t>награжденный отличник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Орнитологи </t>
+  </si>
+  <si>
+    <t>птицеведы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">остеохондрозу </t>
+  </si>
+  <si>
+    <t>эрозия межпозвонковых дисков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">отреагировавшие </t>
+  </si>
+  <si>
+    <t>откликнувшиеся отозвавшиеся</t>
+  </si>
+  <si>
+    <t>оформлением</t>
+  </si>
+  <si>
+    <t>документ  удостоверение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">офтальмологической </t>
+  </si>
+  <si>
+    <t>глазной зрительный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ошеломил </t>
+  </si>
+  <si>
+    <t>поразил ошеломил потряс</t>
+  </si>
+  <si>
+    <t>внеземное зарождение жизни</t>
+  </si>
+  <si>
+    <t>пантаклями</t>
+  </si>
+  <si>
+    <t>знаки обереги талисманы</t>
+  </si>
+  <si>
+    <t>парафинируют</t>
+  </si>
+  <si>
+    <t>наносят парафин  обрабатывают парафином</t>
+  </si>
+  <si>
+    <t xml:space="preserve">партийном </t>
+  </si>
+  <si>
+    <t>партийного направления</t>
+  </si>
+  <si>
+    <t xml:space="preserve">паталогоанатомического </t>
+  </si>
+  <si>
+    <t>изучение болезней после смерти</t>
+  </si>
+  <si>
+    <t>персоналку</t>
+  </si>
+  <si>
+    <t>личный чат личная переписка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">пестицидов </t>
+  </si>
+  <si>
+    <t xml:space="preserve">пиелонефритом </t>
+  </si>
+  <si>
+    <t>воспаление почек</t>
+  </si>
+  <si>
+    <t>пласты</t>
+  </si>
+  <si>
+    <t>слои уровни полосы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">погонах </t>
+  </si>
+  <si>
+    <t>петлицы нашивки знаки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">полимолекулярных </t>
+  </si>
+  <si>
+    <t>полимерных многомолекулярных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">полусекстиля </t>
+  </si>
+  <si>
+    <t>астрологический угол астрологическая связь</t>
+  </si>
+  <si>
+    <t>пост</t>
+  </si>
+  <si>
+    <t>часовой охранник</t>
+  </si>
+  <si>
+    <t>ценник список каталог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">профессор </t>
+  </si>
+  <si>
+    <t>руководитель ученый педагог</t>
+  </si>
+  <si>
+    <t>проформы</t>
+  </si>
+  <si>
+    <t>церемония показуха шаблон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">психолингвистики </t>
+  </si>
+  <si>
+    <t>психология языка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">психологизмом </t>
+  </si>
+  <si>
+    <t>психоанализ</t>
+  </si>
+  <si>
+    <t>психология</t>
+  </si>
+  <si>
+    <t>психика душевность</t>
+  </si>
+  <si>
+    <t>пульсе</t>
+  </si>
+  <si>
+    <t>удар биение частота</t>
+  </si>
+  <si>
+    <t>экстремисты бунтари новаторы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">расфасовываются </t>
+  </si>
+  <si>
+    <t>пакуются фасуются сортируются</t>
+  </si>
+  <si>
+    <t>режим</t>
+  </si>
+  <si>
+    <t>риртуал обряд обычай</t>
+  </si>
+  <si>
+    <t>резюме</t>
+  </si>
+  <si>
+    <t>обзор досье заключение</t>
+  </si>
+  <si>
+    <t>реципиента</t>
+  </si>
+  <si>
+    <t>получатель бенефициар</t>
+  </si>
+  <si>
+    <t>механизм аппарат устройство</t>
+  </si>
+  <si>
+    <t>проза белетристика</t>
+  </si>
+  <si>
+    <t>рупор</t>
+  </si>
+  <si>
+    <t>транслятор агитатор усилитель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сальтаницизма </t>
+  </si>
+  <si>
+    <t>ерунда чушь  глупость</t>
+  </si>
+  <si>
+    <t>светофоре</t>
+  </si>
+  <si>
+    <t>регулировщик</t>
+  </si>
+  <si>
+    <t>секс</t>
+  </si>
+  <si>
+    <t>близость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сексолог </t>
+  </si>
+  <si>
+    <t>консультант по сексуальной жизни</t>
+  </si>
+  <si>
+    <t>сексуальной энергии</t>
+  </si>
+  <si>
+    <t>половая энергия</t>
+  </si>
+  <si>
+    <t>многочасовой фильм</t>
+  </si>
+  <si>
+    <t>связь соединение</t>
+  </si>
+  <si>
+    <t>сканирование</t>
+  </si>
+  <si>
+    <t>цифровое копирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">спеццентрала </t>
+  </si>
+  <si>
+    <t>спеццентр</t>
+  </si>
+  <si>
+    <t>сдерживающего тормозящего</t>
+  </si>
+  <si>
+    <t>вращающуюся</t>
+  </si>
+  <si>
+    <t>вокзал терминал транспортный узел</t>
+  </si>
+  <si>
+    <t>субкультуры</t>
+  </si>
+  <si>
+    <t>молодежные движения  молодежные стили</t>
+  </si>
+  <si>
+    <t xml:space="preserve">суррогатной </t>
+  </si>
+  <si>
+    <t>заместительной поддельной ненастоящей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сутенеров </t>
+  </si>
+  <si>
+    <t>альфонс жигало растовщик</t>
+  </si>
+  <si>
+    <t>сверхсветовых</t>
+  </si>
+  <si>
+    <t>тезка</t>
+  </si>
+  <si>
+    <t>однофамилец двойник</t>
+  </si>
+  <si>
+    <t>боевик на экране</t>
+  </si>
+  <si>
+    <t xml:space="preserve">техническом </t>
+  </si>
+  <si>
+    <t>технологический аппаратный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">техногенной </t>
+  </si>
+  <si>
+    <t>искуственный технологический</t>
+  </si>
+  <si>
+    <t>тордионов</t>
+  </si>
+  <si>
+    <t>олигомеры полимеры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тримеров, тетрамеров, пентамеров </t>
+  </si>
+  <si>
+    <t xml:space="preserve">тромбоцитов </t>
+  </si>
+  <si>
+    <t>кровяные клетки</t>
+  </si>
+  <si>
+    <t>звуковые волны неслышимые человеком</t>
+  </si>
+  <si>
+    <t>невидимый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">фазенды </t>
+  </si>
+  <si>
+    <t>участок  загородный дом  усадьба</t>
+  </si>
+  <si>
+    <t>факультета</t>
+  </si>
+  <si>
+    <t>институт курс академия</t>
+  </si>
+  <si>
+    <t>призрачного невидимого</t>
+  </si>
+  <si>
+    <t xml:space="preserve">фибраналитической </t>
+  </si>
+  <si>
+    <t>фильм</t>
+  </si>
+  <si>
+    <t>кинопоказ</t>
+  </si>
+  <si>
+    <t>флаконы</t>
+  </si>
+  <si>
+    <t>емкость сосуд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">фойе </t>
+  </si>
+  <si>
+    <t>приемная прихожая</t>
+  </si>
+  <si>
+    <t>фотомоделей</t>
+  </si>
+  <si>
+    <t>манекенщицы модели</t>
+  </si>
+  <si>
+    <t>хирургии</t>
+  </si>
+  <si>
+    <t>оперирование</t>
+  </si>
+  <si>
+    <t>генные носители</t>
+  </si>
+  <si>
+    <t xml:space="preserve">хулиганов </t>
+  </si>
+  <si>
+    <t>буйный задира баловник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">цирках </t>
+  </si>
+  <si>
+    <t>арена представление</t>
+  </si>
+  <si>
+    <t>шантажа</t>
+  </si>
+  <si>
+    <t>давление угроза запугивание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">школ </t>
+  </si>
+  <si>
+    <t>учебное заведение</t>
+  </si>
+  <si>
+    <t>натуральная природная органическая</t>
+  </si>
+  <si>
+    <t>оценка предсказание прогнозирование</t>
+  </si>
+  <si>
+    <t>кукольная магия</t>
+  </si>
+  <si>
+    <t>окутывать обертывать</t>
+  </si>
+  <si>
+    <t>мощность сила активность</t>
+  </si>
+  <si>
+    <t>силовой активной динамичной</t>
+  </si>
+  <si>
+    <t>вибрационный  энергетический</t>
+  </si>
+  <si>
+    <t>энергопотенциала</t>
+  </si>
+  <si>
+    <t>энергетический ресурс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">энергоцентр </t>
+  </si>
+  <si>
+    <t>энергоблок электростанция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">эритроцитов </t>
+  </si>
+  <si>
+    <t>красные клетки крови</t>
+  </si>
+  <si>
+    <t xml:space="preserve">этилового </t>
+  </si>
+  <si>
+    <t>винный</t>
+  </si>
+  <si>
+    <t>обеликс</t>
+  </si>
+  <si>
+    <t>монумент</t>
+  </si>
+  <si>
+    <t>статуя памятник</t>
+  </si>
+  <si>
+    <t>ремонтирован</t>
+  </si>
+  <si>
+    <t>восстановлен обновлен</t>
+  </si>
+  <si>
+    <t>сервисах</t>
+  </si>
+  <si>
+    <t>услугах системах приложениях</t>
+  </si>
+  <si>
+    <t>профессионал</t>
+  </si>
+  <si>
+    <t>знаток ценитель опытный</t>
+  </si>
+  <si>
+    <t>багаж</t>
+  </si>
+  <si>
+    <t>кладб посылка барахло</t>
+  </si>
+  <si>
+    <t>кроссворд</t>
+  </si>
+  <si>
+    <t>ребус задача игра</t>
   </si>
 </sst>
 </file>
@@ -3317,11 +4439,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7256F3A-5CBA-4182-B90F-37645EE12738}">
-  <dimension ref="A2:B70"/>
+  <dimension ref="A2:B278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2">
@@ -3488,194 +4610,1899 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="B45" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="B46" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="B47" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
+      <c r="B55" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="B56" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
+      <c r="B57" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="B58" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
+      <c r="B59" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
+      <c r="B60" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="B61" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="B62" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="B68" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="12" t="s">
         <v>910</v>
+      </c>
+      <c r="B70" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>925</v>
+      </c>
+      <c r="B72" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>950</v>
+      </c>
+      <c r="B73" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>952</v>
+      </c>
+      <c r="B75" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>955</v>
+      </c>
+      <c r="B77" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>957</v>
+      </c>
+      <c r="B78" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>959</v>
+      </c>
+      <c r="B79" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>961</v>
+      </c>
+      <c r="B80" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>964</v>
+      </c>
+      <c r="B82" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>966</v>
+      </c>
+      <c r="B83" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>968</v>
+      </c>
+      <c r="B84" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>971</v>
+      </c>
+      <c r="B86" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>41</v>
+      </c>
+      <c r="B88" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>975</v>
+      </c>
+      <c r="B89" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>977</v>
+      </c>
+      <c r="B90" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>979</v>
+      </c>
+      <c r="B91" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>981</v>
+      </c>
+      <c r="B92" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>983</v>
+      </c>
+      <c r="B93" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>64</v>
+      </c>
+      <c r="B94" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>986</v>
+      </c>
+      <c r="B95" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>988</v>
+      </c>
+      <c r="B96" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>61</v>
+      </c>
+      <c r="B97" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>51</v>
+      </c>
+      <c r="B98" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>53</v>
+      </c>
+      <c r="B100" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>994</v>
+      </c>
+      <c r="B101" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>996</v>
+      </c>
+      <c r="B102" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>998</v>
+      </c>
+      <c r="B103" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>467</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>36</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>18</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>44</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>50</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>71</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>952</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>52</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>26</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>42</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>46</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>68</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>77</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>49</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>65</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>30</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>69</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>58</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>55</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>59</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" t="s">
+        <v>34</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>458</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>594</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" t="s">
+        <v>56</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" t="s">
+        <v>43</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" t="s">
+        <v>78</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
+        <v>466</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" t="s">
+        <v>60</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>32</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>14</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" t="s">
+        <v>28</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" t="s">
+        <v>13</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" t="s">
+        <v>595</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>73</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" t="s">
+        <v>70</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" t="s">
+        <v>47</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" t="s">
+        <v>72</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" t="s">
+        <v>67</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" t="s">
+        <v>4</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" t="s">
+        <v>435</v>
+      </c>
+      <c r="B264" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" t="s">
+        <v>63</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" t="s">
+        <v>35</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" t="s">
+        <v>2</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B268" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B269" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B270" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B271" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B275" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B278" t="s">
+        <v>1298</v>
       </c>
     </row>
   </sheetData>
